--- a/LPR.xlsx
+++ b/LPR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ztemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE66187-9A7F-41D3-BFAB-D6AA0BFC9335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5439ED-63CA-4F8A-859E-667C58FC3405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5E6CEC65-BF63-43C9-BE49-625E365FE642}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="1609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="2043">
   <si>
     <t>HR</t>
   </si>
@@ -4910,6 +4910,1312 @@
   </si>
   <si>
     <t>0975556801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jigglypuff
+ </t>
+  </si>
+  <si>
+    <t>鄭凱恩</t>
+  </si>
+  <si>
+    <t>Kai En</t>
+  </si>
+  <si>
+    <t>K22028</t>
+  </si>
+  <si>
+    <t>許玹菲</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>K22030</t>
+  </si>
+  <si>
+    <t>黎恩</t>
+  </si>
+  <si>
+    <t>Lyen</t>
+  </si>
+  <si>
+    <t>K22023</t>
+  </si>
+  <si>
+    <t>李墨</t>
+  </si>
+  <si>
+    <t>Nemo</t>
+  </si>
+  <si>
+    <t>K21025</t>
+  </si>
+  <si>
+    <t>陳葇均</t>
+  </si>
+  <si>
+    <t>Regina</t>
+  </si>
+  <si>
+    <t>K21028</t>
+  </si>
+  <si>
+    <t>羅紹軒</t>
+  </si>
+  <si>
+    <t>K22024</t>
+  </si>
+  <si>
+    <t>康特華</t>
+  </si>
+  <si>
+    <t>Kang</t>
+  </si>
+  <si>
+    <t>K21036</t>
+  </si>
+  <si>
+    <t>陳芯琂</t>
+  </si>
+  <si>
+    <t>Yuma</t>
+  </si>
+  <si>
+    <t>K22025</t>
+  </si>
+  <si>
+    <t>許學讓</t>
+  </si>
+  <si>
+    <t>Ronnie</t>
+  </si>
+  <si>
+    <t>K22026</t>
+  </si>
+  <si>
+    <t>張又予</t>
+  </si>
+  <si>
+    <t>Morgan</t>
+  </si>
+  <si>
+    <t>K22027</t>
+  </si>
+  <si>
+    <t>簡瑞彥</t>
+  </si>
+  <si>
+    <t>K21032</t>
+  </si>
+  <si>
+    <t>林洛瑜</t>
+  </si>
+  <si>
+    <t>K21033</t>
+  </si>
+  <si>
+    <t>林楚芫</t>
+  </si>
+  <si>
+    <t>Yvette</t>
+  </si>
+  <si>
+    <t>K22012</t>
+  </si>
+  <si>
+    <t>黃宣捷</t>
+  </si>
+  <si>
+    <t>Jale</t>
+  </si>
+  <si>
+    <t>K22016</t>
+  </si>
+  <si>
+    <t>楊軒帆</t>
+  </si>
+  <si>
+    <t>Val</t>
+  </si>
+  <si>
+    <t>K22015</t>
+  </si>
+  <si>
+    <t>李玧翧</t>
+  </si>
+  <si>
+    <t>Kingbo</t>
+  </si>
+  <si>
+    <t>K22017</t>
+  </si>
+  <si>
+    <t>曾沛浠</t>
+  </si>
+  <si>
+    <t>K22019</t>
+  </si>
+  <si>
+    <t>王禹倢</t>
+  </si>
+  <si>
+    <t>Riley</t>
+  </si>
+  <si>
+    <t>K22020</t>
+  </si>
+  <si>
+    <t>楊人碩</t>
+  </si>
+  <si>
+    <t>Sho</t>
+  </si>
+  <si>
+    <t>K22021</t>
+  </si>
+  <si>
+    <t>賴玥君</t>
+  </si>
+  <si>
+    <t>K22032</t>
+  </si>
+  <si>
+    <t>陳圓萱</t>
+  </si>
+  <si>
+    <t>Jessie</t>
+  </si>
+  <si>
+    <t>K22044</t>
+  </si>
+  <si>
+    <t>曾楷棣</t>
+  </si>
+  <si>
+    <t>Artuś</t>
+  </si>
+  <si>
+    <t>K22050</t>
+  </si>
+  <si>
+    <t>鍾祤甯</t>
+  </si>
+  <si>
+    <t>Mollie</t>
+  </si>
+  <si>
+    <t>K22048</t>
+  </si>
+  <si>
+    <t>蔡沐承</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Cai</t>
+  </si>
+  <si>
+    <t>K22049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumpluff
+ </t>
+  </si>
+  <si>
+    <t>韓云曜</t>
+  </si>
+  <si>
+    <t>Alston</t>
+  </si>
+  <si>
+    <t>Han</t>
+  </si>
+  <si>
+    <t>K22013</t>
+  </si>
+  <si>
+    <t>彭弈甯</t>
+  </si>
+  <si>
+    <t>Orla</t>
+  </si>
+  <si>
+    <t>K22035</t>
+  </si>
+  <si>
+    <t>陳梓馨</t>
+  </si>
+  <si>
+    <t>K23014</t>
+  </si>
+  <si>
+    <t>池沛璇</t>
+  </si>
+  <si>
+    <t>Gigi</t>
+  </si>
+  <si>
+    <t>K22034</t>
+  </si>
+  <si>
+    <t>楊之予</t>
+  </si>
+  <si>
+    <t>Jocelyn</t>
+  </si>
+  <si>
+    <t>K23010</t>
+  </si>
+  <si>
+    <t>黃禾蘊</t>
+  </si>
+  <si>
+    <t>Ausha</t>
+  </si>
+  <si>
+    <t>K23016</t>
+  </si>
+  <si>
+    <t>林渝恩</t>
+  </si>
+  <si>
+    <t>K22046</t>
+  </si>
+  <si>
+    <t>王羚妃</t>
+  </si>
+  <si>
+    <t>Miffy</t>
+  </si>
+  <si>
+    <t>K23012</t>
+  </si>
+  <si>
+    <t>黃靖</t>
+  </si>
+  <si>
+    <t>Toby</t>
+  </si>
+  <si>
+    <t>K23004</t>
+  </si>
+  <si>
+    <t>梁語栗</t>
+  </si>
+  <si>
+    <t>K22037</t>
+  </si>
+  <si>
+    <t>陳星尹</t>
+  </si>
+  <si>
+    <t>Kimberly</t>
+  </si>
+  <si>
+    <t>K22038</t>
+  </si>
+  <si>
+    <t>余姝瑤</t>
+  </si>
+  <si>
+    <t>Yu</t>
+  </si>
+  <si>
+    <t>K22039</t>
+  </si>
+  <si>
+    <t>余沬瑤</t>
+  </si>
+  <si>
+    <t>K22040</t>
+  </si>
+  <si>
+    <t>林妍菲</t>
+  </si>
+  <si>
+    <t>Faith</t>
+  </si>
+  <si>
+    <t>K22041</t>
+  </si>
+  <si>
+    <t>張紘睿</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>K23002</t>
+  </si>
+  <si>
+    <t>李擇</t>
+  </si>
+  <si>
+    <t>Azariah</t>
+  </si>
+  <si>
+    <t>K23001</t>
+  </si>
+  <si>
+    <t>黃默容</t>
+  </si>
+  <si>
+    <t>Connor</t>
+  </si>
+  <si>
+    <t>K23017</t>
+  </si>
+  <si>
+    <t>黃臻芮</t>
+  </si>
+  <si>
+    <t>Jennie</t>
+  </si>
+  <si>
+    <t>K23003</t>
+  </si>
+  <si>
+    <t>何品萱</t>
+  </si>
+  <si>
+    <t>Sharon</t>
+  </si>
+  <si>
+    <t>K23006</t>
+  </si>
+  <si>
+    <t>宋禹霏</t>
+  </si>
+  <si>
+    <t>Quenna</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>K22045</t>
+  </si>
+  <si>
+    <t>江梓睿</t>
+  </si>
+  <si>
+    <t>Kong</t>
+  </si>
+  <si>
+    <t>K23011</t>
+  </si>
+  <si>
+    <t>林邱鍏</t>
+  </si>
+  <si>
+    <t>Lin Chiu</t>
+  </si>
+  <si>
+    <t>K23009</t>
+  </si>
+  <si>
+    <t>福孝恂</t>
+  </si>
+  <si>
+    <t>Figueroa Soong</t>
+  </si>
+  <si>
+    <t>K23013</t>
+  </si>
+  <si>
+    <t>黃楷峻</t>
+  </si>
+  <si>
+    <t>Poki</t>
+  </si>
+  <si>
+    <t>K23015</t>
+  </si>
+  <si>
+    <t>李沐宸</t>
+  </si>
+  <si>
+    <t>Effie</t>
+  </si>
+  <si>
+    <t>K23007</t>
+  </si>
+  <si>
+    <t>林煦容</t>
+  </si>
+  <si>
+    <t>Ryle</t>
+  </si>
+  <si>
+    <t>K23008</t>
+  </si>
+  <si>
+    <t>林湘</t>
+  </si>
+  <si>
+    <t>Sharni</t>
+  </si>
+  <si>
+    <t>K22047</t>
+  </si>
+  <si>
+    <t>黃詠晴</t>
+  </si>
+  <si>
+    <t>Sunny</t>
+  </si>
+  <si>
+    <t>K23005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoopa
+ </t>
+  </si>
+  <si>
+    <t>簡資浠</t>
+  </si>
+  <si>
+    <t>K21011</t>
+  </si>
+  <si>
+    <t>趙威棋</t>
+  </si>
+  <si>
+    <t>Wiki</t>
+  </si>
+  <si>
+    <t>Chao</t>
+  </si>
+  <si>
+    <t>K20021</t>
+  </si>
+  <si>
+    <t>林承軒</t>
+  </si>
+  <si>
+    <t>K21030</t>
+  </si>
+  <si>
+    <t>劉嘉昀</t>
+  </si>
+  <si>
+    <t>K20018</t>
+  </si>
+  <si>
+    <t>沈妍榛</t>
+  </si>
+  <si>
+    <t>K19029</t>
+  </si>
+  <si>
+    <t>蔡和栩</t>
+  </si>
+  <si>
+    <t>Hendrick</t>
+  </si>
+  <si>
+    <t>K21040</t>
+  </si>
+  <si>
+    <t>林偊諾</t>
+  </si>
+  <si>
+    <t>Jinno</t>
+  </si>
+  <si>
+    <t>K21002</t>
+  </si>
+  <si>
+    <t>張紘赫</t>
+  </si>
+  <si>
+    <t>Morris</t>
+  </si>
+  <si>
+    <t>K21013</t>
+  </si>
+  <si>
+    <t>方丞懿</t>
+  </si>
+  <si>
+    <t>Fang</t>
+  </si>
+  <si>
+    <t>K21014</t>
+  </si>
+  <si>
+    <t>呂昕宬</t>
+  </si>
+  <si>
+    <t>Avery</t>
+  </si>
+  <si>
+    <t>K21038</t>
+  </si>
+  <si>
+    <t>黃晨瑄</t>
+  </si>
+  <si>
+    <t>Shanna</t>
+  </si>
+  <si>
+    <t>K21019</t>
+  </si>
+  <si>
+    <t>陳楷軒</t>
+  </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>K21008</t>
+  </si>
+  <si>
+    <t>蘇柏豪</t>
+  </si>
+  <si>
+    <t>K21001</t>
+  </si>
+  <si>
+    <t>吳宏鈞</t>
+  </si>
+  <si>
+    <t>Herman</t>
+  </si>
+  <si>
+    <t>K21009</t>
+  </si>
+  <si>
+    <t>鄭翃軒</t>
+  </si>
+  <si>
+    <t>K21005</t>
+  </si>
+  <si>
+    <t>福孝惇</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>K21018</t>
+  </si>
+  <si>
+    <t>李穆</t>
+  </si>
+  <si>
+    <t>Muller</t>
+  </si>
+  <si>
+    <t>K20030</t>
+  </si>
+  <si>
+    <t>林睿恩</t>
+  </si>
+  <si>
+    <t>K21016</t>
+  </si>
+  <si>
+    <t>賴苡安</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>K21004</t>
+  </si>
+  <si>
+    <t>呂鎮東</t>
+  </si>
+  <si>
+    <t>Christopher</t>
+  </si>
+  <si>
+    <t>K21006</t>
+  </si>
+  <si>
+    <t>陳君瑜</t>
+  </si>
+  <si>
+    <t>Falon</t>
+  </si>
+  <si>
+    <t>K20036</t>
+  </si>
+  <si>
+    <t>周芮璿</t>
+  </si>
+  <si>
+    <t>K21017</t>
+  </si>
+  <si>
+    <t>郭芯妍</t>
+  </si>
+  <si>
+    <t>Layla</t>
+  </si>
+  <si>
+    <t>K20031</t>
+  </si>
+  <si>
+    <t>李昂謙</t>
+  </si>
+  <si>
+    <t>K20032</t>
+  </si>
+  <si>
+    <t>沈博承</t>
+  </si>
+  <si>
+    <t>Boyce</t>
+  </si>
+  <si>
+    <t>K21010</t>
+  </si>
+  <si>
+    <t>許軒齊</t>
+  </si>
+  <si>
+    <t>Xu</t>
+  </si>
+  <si>
+    <t>K21007</t>
+  </si>
+  <si>
+    <t>楊子宏</t>
+  </si>
+  <si>
+    <t>Theodore</t>
+  </si>
+  <si>
+    <t>K21031</t>
+  </si>
+  <si>
+    <t>陳畇菲</t>
+  </si>
+  <si>
+    <t>Mira</t>
+  </si>
+  <si>
+    <t>K21035</t>
+  </si>
+  <si>
+    <t>吳子龍</t>
+  </si>
+  <si>
+    <t>K20037</t>
+  </si>
+  <si>
+    <t>闕稟宸</t>
+  </si>
+  <si>
+    <t>Izack</t>
+  </si>
+  <si>
+    <t>K21037</t>
+  </si>
+  <si>
+    <t>姜守怡</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Cormaci</t>
+  </si>
+  <si>
+    <t>K20038</t>
+  </si>
+  <si>
+    <t>陳凝萱</t>
+  </si>
+  <si>
+    <t>Ning</t>
+  </si>
+  <si>
+    <t>K21041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haunter
+ </t>
+  </si>
+  <si>
+    <t>林星澄</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
+  <si>
+    <t>K22011</t>
+  </si>
+  <si>
+    <t>林華煦</t>
+  </si>
+  <si>
+    <t>Kayden</t>
+  </si>
+  <si>
+    <t>K22008</t>
+  </si>
+  <si>
+    <t>柳羿璿</t>
+  </si>
+  <si>
+    <t>Elroy Liu</t>
+  </si>
+  <si>
+    <t>K22029</t>
+  </si>
+  <si>
+    <t>宣又菲</t>
+  </si>
+  <si>
+    <t>Fei</t>
+  </si>
+  <si>
+    <t>Hsuan</t>
+  </si>
+  <si>
+    <t>K21022</t>
+  </si>
+  <si>
+    <t>曹懷洋</t>
+  </si>
+  <si>
+    <t>Abraham</t>
+  </si>
+  <si>
+    <t>K22002</t>
+  </si>
+  <si>
+    <t>吳嬡妮</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>K22003</t>
+  </si>
+  <si>
+    <t>林婕希</t>
+  </si>
+  <si>
+    <t>K21015</t>
+  </si>
+  <si>
+    <t>劉芷妍</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>K21024</t>
+  </si>
+  <si>
+    <t>鄧丞恩</t>
+  </si>
+  <si>
+    <t>K22004</t>
+  </si>
+  <si>
+    <t>王婕妍</t>
+  </si>
+  <si>
+    <t>Jamie</t>
+  </si>
+  <si>
+    <t>K22005</t>
+  </si>
+  <si>
+    <t>陳翊豪</t>
+  </si>
+  <si>
+    <t>K21020</t>
+  </si>
+  <si>
+    <t>黃亞淇</t>
+  </si>
+  <si>
+    <t>Archie</t>
+  </si>
+  <si>
+    <t>K21021</t>
+  </si>
+  <si>
+    <t>郭欣晏</t>
+  </si>
+  <si>
+    <t>Tali</t>
+  </si>
+  <si>
+    <t>K22010</t>
+  </si>
+  <si>
+    <t>王詩堤</t>
+  </si>
+  <si>
+    <t>Teo</t>
+  </si>
+  <si>
+    <t>K22006</t>
+  </si>
+  <si>
+    <t>曾禹喆</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>K22009</t>
+  </si>
+  <si>
+    <t>黃丞霏</t>
+  </si>
+  <si>
+    <t>Nana</t>
+  </si>
+  <si>
+    <t>K22007</t>
+  </si>
+  <si>
+    <t>林彥甫</t>
+  </si>
+  <si>
+    <t>Freddy</t>
+  </si>
+  <si>
+    <t>K21023</t>
+  </si>
+  <si>
+    <t>賴羿君</t>
+  </si>
+  <si>
+    <t>Luca</t>
+  </si>
+  <si>
+    <t>K22033</t>
+  </si>
+  <si>
+    <t>戴瑋廷</t>
+  </si>
+  <si>
+    <t>Alistar</t>
+  </si>
+  <si>
+    <t>Dai</t>
+  </si>
+  <si>
+    <t>K22043</t>
+  </si>
+  <si>
+    <t>何彧安</t>
+  </si>
+  <si>
+    <t>Aston</t>
+  </si>
+  <si>
+    <t>K22042</t>
+  </si>
+  <si>
+    <t>蘇子程</t>
+  </si>
+  <si>
+    <t>Ruben</t>
+  </si>
+  <si>
+    <t>K21039</t>
+  </si>
+  <si>
+    <t>0987960969</t>
+  </si>
+  <si>
+    <t>0923346707</t>
+  </si>
+  <si>
+    <t>0952177077</t>
+  </si>
+  <si>
+    <t>0952909771</t>
+  </si>
+  <si>
+    <t>0978075663</t>
+  </si>
+  <si>
+    <t>0952306899</t>
+  </si>
+  <si>
+    <t>0937970303</t>
+  </si>
+  <si>
+    <t>0922004977</t>
+  </si>
+  <si>
+    <t>0968119913</t>
+  </si>
+  <si>
+    <t>0966437682</t>
+  </si>
+  <si>
+    <t>0986663771</t>
+  </si>
+  <si>
+    <t>0911184723</t>
+  </si>
+  <si>
+    <t>0930684648</t>
+  </si>
+  <si>
+    <t>0911640998</t>
+  </si>
+  <si>
+    <t>0909205536</t>
+  </si>
+  <si>
+    <t>0976298421</t>
+  </si>
+  <si>
+    <t>0989426621</t>
+  </si>
+  <si>
+    <t>0988865021</t>
+  </si>
+  <si>
+    <t>0988373873</t>
+  </si>
+  <si>
+    <t>0913563989</t>
+  </si>
+  <si>
+    <t>0916872090</t>
+  </si>
+  <si>
+    <t>0933328708</t>
+  </si>
+  <si>
+    <t>0979571517</t>
+  </si>
+  <si>
+    <t>0910520222</t>
+  </si>
+  <si>
+    <t>0981950887</t>
+  </si>
+  <si>
+    <t>0916490789</t>
+  </si>
+  <si>
+    <t>0930811853</t>
+  </si>
+  <si>
+    <t>0972775992</t>
+  </si>
+  <si>
+    <t>0910097476</t>
+  </si>
+  <si>
+    <t>0910972087</t>
+  </si>
+  <si>
+    <t>0975587613</t>
+  </si>
+  <si>
+    <t>0968085588</t>
+  </si>
+  <si>
+    <t>0981181050</t>
+  </si>
+  <si>
+    <t>0989173047</t>
+  </si>
+  <si>
+    <t>0989138668</t>
+  </si>
+  <si>
+    <t>0933152976</t>
+  </si>
+  <si>
+    <t>0922901585</t>
+  </si>
+  <si>
+    <t>0982734611</t>
+  </si>
+  <si>
+    <t>0982269624</t>
+  </si>
+  <si>
+    <t>0921196501</t>
+  </si>
+  <si>
+    <t>0960626742</t>
+  </si>
+  <si>
+    <t>0986888601</t>
+  </si>
+  <si>
+    <t>0975021990</t>
+  </si>
+  <si>
+    <t>0978472903</t>
+  </si>
+  <si>
+    <t>0933888642</t>
+  </si>
+  <si>
+    <t>0922821106</t>
+  </si>
+  <si>
+    <t>0909305908</t>
+  </si>
+  <si>
+    <t>0987524271</t>
+  </si>
+  <si>
+    <t>0970697300</t>
+  </si>
+  <si>
+    <t>0911955534</t>
+  </si>
+  <si>
+    <t>0978968330</t>
+  </si>
+  <si>
+    <t>0910474301</t>
+  </si>
+  <si>
+    <t>0919638647</t>
+  </si>
+  <si>
+    <t>0921588753</t>
+  </si>
+  <si>
+    <t>0914072118</t>
+  </si>
+  <si>
+    <t>0921326189</t>
+  </si>
+  <si>
+    <t>0919607589</t>
+  </si>
+  <si>
+    <t>0978246857</t>
+  </si>
+  <si>
+    <t>0935223320</t>
+  </si>
+  <si>
+    <t>0922391119</t>
+  </si>
+  <si>
+    <t>0910838730</t>
+  </si>
+  <si>
+    <t>0926805947</t>
+  </si>
+  <si>
+    <t>0932733492</t>
+  </si>
+  <si>
+    <t>0987514430</t>
+  </si>
+  <si>
+    <t>0929039720</t>
+  </si>
+  <si>
+    <t>0970540592</t>
+  </si>
+  <si>
+    <t>0988756671</t>
+  </si>
+  <si>
+    <t>0972096693</t>
+  </si>
+  <si>
+    <t>0970007234</t>
+  </si>
+  <si>
+    <t>0955421270</t>
+  </si>
+  <si>
+    <t>0988236320</t>
+  </si>
+  <si>
+    <t>0952085255</t>
+  </si>
+  <si>
+    <t>0968678808</t>
+  </si>
+  <si>
+    <t>0916806189</t>
+  </si>
+  <si>
+    <t>0953-571903</t>
+  </si>
+  <si>
+    <t>0970110087</t>
+  </si>
+  <si>
+    <t>0956119233</t>
+  </si>
+  <si>
+    <t>0988055631</t>
+  </si>
+  <si>
+    <t>0911074926</t>
+  </si>
+  <si>
+    <t>0972879134</t>
+  </si>
+  <si>
+    <t>0916138365</t>
+  </si>
+  <si>
+    <t>0972339809</t>
+  </si>
+  <si>
+    <t>0911789885</t>
+  </si>
+  <si>
+    <t>0978673667</t>
+  </si>
+  <si>
+    <t>0935112371</t>
+  </si>
+  <si>
+    <t>0972464471</t>
+  </si>
+  <si>
+    <t>0938780019</t>
+  </si>
+  <si>
+    <t>0955042350</t>
+  </si>
+  <si>
+    <t>0955230555</t>
+  </si>
+  <si>
+    <t>0988856551</t>
+  </si>
+  <si>
+    <t>0987516607</t>
+  </si>
+  <si>
+    <t>0912802179</t>
+  </si>
+  <si>
+    <t>0912328137</t>
+  </si>
+  <si>
+    <t>0975388701</t>
+  </si>
+  <si>
+    <t>0976219517</t>
+  </si>
+  <si>
+    <t>0963235947</t>
+  </si>
+  <si>
+    <t>0972855824</t>
+  </si>
+  <si>
+    <t>0910343243</t>
+  </si>
+  <si>
+    <t>0900123573</t>
+  </si>
+  <si>
+    <t>0901032156</t>
+  </si>
+  <si>
+    <t>0918633156</t>
+  </si>
+  <si>
+    <t>0921225785</t>
+  </si>
+  <si>
+    <t>0988007169</t>
+  </si>
+  <si>
+    <t>0912368050</t>
+  </si>
+  <si>
+    <t>0978703632</t>
+  </si>
+  <si>
+    <t>0955751908</t>
+  </si>
+  <si>
+    <t>0963633009</t>
+  </si>
+  <si>
+    <t>0930890009</t>
+  </si>
+  <si>
+    <t>0958386799</t>
+  </si>
+  <si>
+    <t>0952037373</t>
+  </si>
+  <si>
+    <t>0928805506</t>
+  </si>
+  <si>
+    <t>0939726829</t>
+  </si>
+  <si>
+    <t>0987365775</t>
+  </si>
+  <si>
+    <t>0978793297</t>
+  </si>
+  <si>
+    <t>0977247000</t>
+  </si>
+  <si>
+    <t>0925612260</t>
+  </si>
+  <si>
+    <t>0975308896</t>
+  </si>
+  <si>
+    <t>0932345512</t>
+  </si>
+  <si>
+    <t>0931137979</t>
+  </si>
+  <si>
+    <t>0922502112</t>
+  </si>
+  <si>
+    <t>0909006020</t>
+  </si>
+  <si>
+    <t>0922707199</t>
+  </si>
+  <si>
+    <t>0920221214</t>
+  </si>
+  <si>
+    <t>0930318162</t>
+  </si>
+  <si>
+    <t>0955008253</t>
+  </si>
+  <si>
+    <t>0933924925</t>
+  </si>
+  <si>
+    <t>0975795004</t>
+  </si>
+  <si>
+    <t>0975817797</t>
+  </si>
+  <si>
+    <t>0921830323</t>
+  </si>
+  <si>
+    <t>0912576012</t>
   </si>
 </sst>
 </file>
@@ -5312,14 +6618,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C6FD721-7C36-4049-B693-FB8DFDC86D2A}">
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="5" bestFit="1" customWidth="1"/>
   </cols>
@@ -13326,6 +14632,2421 @@
       </c>
       <c r="G348" s="5" t="s">
         <v>1608</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A349" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E349" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="F349" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G349" s="5" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A350" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E350" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F350" s="5" t="s">
+        <v>1915</v>
+      </c>
+      <c r="G350" s="5" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D351" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E351" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F351" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G351" s="5" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E352" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F352" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G352" s="5" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A353" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E353" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F353" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G353" s="5" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A354" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E354" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F354" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G354" s="5" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A355" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E355" s="4" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F355" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G355" s="5" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A356" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E356" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F356" s="5" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G356" s="5" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A357" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E357" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F357" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G357" s="5" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A358" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E358" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F358" s="5" t="s">
+        <v>1927</v>
+      </c>
+      <c r="G358" s="5" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E359" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="F359" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G359" s="5" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E360" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F360" s="5" t="s">
+        <v>1930</v>
+      </c>
+      <c r="G360" s="5" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A361" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E361" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F361" s="5" t="s">
+        <v>1932</v>
+      </c>
+      <c r="G361" s="5" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D362" s="4" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E362" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F362" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G362" s="5" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A363" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E363" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F363" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G363" s="5" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A364" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E364" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F364" s="5" t="s">
+        <v>1934</v>
+      </c>
+      <c r="G364" s="5" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A365" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="E365" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F365" s="5" t="s">
+        <v>1936</v>
+      </c>
+      <c r="G365" s="5" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A366" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E366" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F366" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G366" s="5" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A367" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E367" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F367" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G367" s="5" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="E368" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F368" s="5" t="s">
+        <v>1942</v>
+      </c>
+      <c r="G368" s="5" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E369" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="F369" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G369" s="5" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E370" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F370" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G370" s="5" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E371" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="F371" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G371" s="5" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A372" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E372" s="4" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F372" s="5" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G372" s="5" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A373" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E373" s="4" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F373" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G373" s="5" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E374" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F374" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G374" s="5" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A375" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E375" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F375" s="5" t="s">
+        <v>1948</v>
+      </c>
+      <c r="G375" s="5" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D376" s="4" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E376" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="F376" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G376" s="5" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E377" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F377" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G377" s="5" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E378" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F378" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G378" s="5" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D379" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E379" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F379" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G379" s="5" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E380" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F380" s="5" t="s">
+        <v>1953</v>
+      </c>
+      <c r="G380" s="5" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E381" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F381" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G381" s="5" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="E382" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F382" s="5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G382" s="5" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E383" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F383" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G383" s="5" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E384" s="4" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F384" s="5" t="s">
+        <v>1959</v>
+      </c>
+      <c r="G384" s="5" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A385" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="E385" s="4" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F385" s="5" t="s">
+        <v>1959</v>
+      </c>
+      <c r="G385" s="5" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E386" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F386" s="5" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G386" s="5" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A387" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E387" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F387" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G387" s="5" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E388" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="F388" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G388" s="5" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A389" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E389" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F389" s="5" t="s">
+        <v>1962</v>
+      </c>
+      <c r="G389" s="5" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A390" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D390" s="4" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E390" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F390" s="5" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G390" s="5" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A391" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C391" s="4" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E391" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F391" s="5" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G391" s="5" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A392" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D392" s="4" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E392" s="4" t="s">
+        <v>1735</v>
+      </c>
+      <c r="F392" s="5" t="s">
+        <v>1966</v>
+      </c>
+      <c r="G392" s="5" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A393" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C393" s="4" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D393" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="E393" s="4" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F393" s="5" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G393" s="5" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A394" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="E394" s="4" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F394" s="5" t="s">
+        <v>1970</v>
+      </c>
+      <c r="G394" s="5" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A395" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="E395" s="4" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F395" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="G395" s="5" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A396" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>1747</v>
+      </c>
+      <c r="E396" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F396" s="5" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G396" s="5" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A397" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E397" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F397" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="G397" s="5" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A398" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D398" s="4" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E398" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F398" s="5" t="s">
+        <v>1977</v>
+      </c>
+      <c r="G398" s="5" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A399" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D399" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E399" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F399" s="5" t="s">
+        <v>1979</v>
+      </c>
+      <c r="G399" s="5" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A400" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D400" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E400" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F400" s="5" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G400" s="5" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A401" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D401" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E401" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="F401" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G401" s="5" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A402" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E402" s="4" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F402" s="5" t="s">
+        <v>1983</v>
+      </c>
+      <c r="G402" s="5" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A403" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E403" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F403" s="5" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G403" s="5" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A404" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E404" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F404" s="5" t="s">
+        <v>1987</v>
+      </c>
+      <c r="G404" s="5" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A405" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="E405" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F405" s="5" t="s">
+        <v>1989</v>
+      </c>
+      <c r="G405" s="5" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A406" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E406" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F406" s="5" t="s">
+        <v>1991</v>
+      </c>
+      <c r="G406" s="5" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A407" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E407" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F407" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G407" s="5" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E408" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F408" s="5" t="s">
+        <v>1927</v>
+      </c>
+      <c r="G408" s="5" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A409" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="E409" s="4" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F409" s="5" t="s">
+        <v>1993</v>
+      </c>
+      <c r="G409" s="5" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A410" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C410" s="4" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E410" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="F410" s="5" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G410" s="5" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C411" s="4" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E411" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F411" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G411" s="5" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E412" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F412" s="5" t="s">
+        <v>1996</v>
+      </c>
+      <c r="G412" s="5" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C413" s="4" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="E413" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="F413" s="5" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G413" s="5" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E414" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F414" s="5" t="s">
+        <v>1998</v>
+      </c>
+      <c r="G414" s="5" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C415" s="4" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="E415" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="F415" s="5" t="s">
+        <v>2000</v>
+      </c>
+      <c r="G415" s="5" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A416" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E416" s="4" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F416" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="G416" s="5" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A417" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>1806</v>
+      </c>
+      <c r="E417" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F417" s="5" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G417" s="5" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A418" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E418" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F418" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="G418" s="5" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E419" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F419" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="G419" s="5" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A420" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>1814</v>
+      </c>
+      <c r="E420" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="F420" s="5" t="s">
+        <v>2006</v>
+      </c>
+      <c r="G420" s="5" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A421" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E421" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F421" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G421" s="5" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A422" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E422" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F422" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G422" s="5" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A423" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="E423" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="F423" s="5" t="s">
+        <v>2008</v>
+      </c>
+      <c r="G423" s="5" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A424" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E424" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F424" s="5" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G424" s="5" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A425" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E425" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F425" s="5" t="s">
+        <v>1989</v>
+      </c>
+      <c r="G425" s="5" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A426" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E426" s="4" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F426" s="5" t="s">
+        <v>2012</v>
+      </c>
+      <c r="G426" s="5" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E427" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F427" s="5" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G427" s="5" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A428" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E428" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F428" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G428" s="5" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E429" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F429" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G429" s="5" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A430" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E430" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="F430" s="5" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G430" s="5" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A431" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E431" s="4" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F431" s="5" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G431" s="5" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A432" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D432" s="4" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E432" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F432" s="5" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G432" s="5" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A433" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E433" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F433" s="5" t="s">
+        <v>2017</v>
+      </c>
+      <c r="G433" s="5" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A434" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E434" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F434" s="5" t="s">
+        <v>2019</v>
+      </c>
+      <c r="G434" s="5" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A435" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E435" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F435" s="5" t="s">
+        <v>2021</v>
+      </c>
+      <c r="G435" s="5" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A436" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D436" s="4" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E436" s="4" t="s">
+        <v>1862</v>
+      </c>
+      <c r="F436" s="5" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G436" s="5" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A437" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E437" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F437" s="5" t="s">
+        <v>2025</v>
+      </c>
+      <c r="G437" s="5" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A438" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E438" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F438" s="5" t="s">
+        <v>2027</v>
+      </c>
+      <c r="G438" s="5" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A439" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E439" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F439" s="5" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G439" s="5" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A440" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C440" s="4" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D440" s="4" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E440" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F440" s="5" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G440" s="5" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A441" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C441" s="4" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="E441" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="F441" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G441" s="5" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A442" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C442" s="4" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>1878</v>
+      </c>
+      <c r="E442" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F442" s="5" t="s">
+        <v>2033</v>
+      </c>
+      <c r="G442" s="5" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A443" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C443" s="4" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E443" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F443" s="5" t="s">
+        <v>2035</v>
+      </c>
+      <c r="G443" s="5" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A444" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B444" s="4" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C444" s="4" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>1883</v>
+      </c>
+      <c r="E444" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F444" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G444" s="5" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A445" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E445" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="F445" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G445" s="5" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A446" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B446" s="4" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C446" s="4" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E446" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F446" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G446" s="5" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A447" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B447" s="4" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C447" s="4" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>1892</v>
+      </c>
+      <c r="E447" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F447" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G447" s="5" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A448" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B448" s="4" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C448" s="4" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E448" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F448" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G448" s="5" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A449" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C449" s="4" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E449" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F449" s="5" t="s">
+        <v>2037</v>
+      </c>
+      <c r="G449" s="5" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A450" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C450" s="4" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E450" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F450" s="5" t="s">
+        <v>1942</v>
+      </c>
+      <c r="G450" s="5" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A451" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C451" s="4" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E451" s="4" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F451" s="5" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G451" s="5" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A452" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C452" s="4" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>1908</v>
+      </c>
+      <c r="E452" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F452" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G452" s="5" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A453" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C453" s="4" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E453" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="F453" s="5" t="s">
+        <v>2041</v>
+      </c>
+      <c r="G453" s="5" t="s">
+        <v>2042</v>
       </c>
     </row>
   </sheetData>

--- a/LPR.xlsx
+++ b/LPR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD85A7C-107F-46D8-97E3-923A64353DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90EA8BD-D84F-4CFF-9FF3-4E3E55CF16E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5E6CEC65-BF63-43C9-BE49-625E365FE642}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3170" uniqueCount="2043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="2044">
   <si>
     <t>HR</t>
   </si>
@@ -6216,6 +6216,10 @@
   </si>
   <si>
     <t>0912576012</t>
+  </si>
+  <si>
+    <t>0912249226</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6285,7 +6289,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6300,9 +6304,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6626,8 +6627,8 @@
     <col min="3" max="3" width="7.5" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6646,10 +6647,10 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>717</v>
       </c>
     </row>
@@ -6669,10 +6670,10 @@
       <c r="E2" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="2" t="s">
         <v>1913</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>1914</v>
       </c>
     </row>
@@ -6692,10 +6693,10 @@
       <c r="E3" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>1915</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="2" t="s">
         <v>1916</v>
       </c>
     </row>
@@ -6715,10 +6716,10 @@
       <c r="E4" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>1917</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="2" t="s">
         <v>1918</v>
       </c>
     </row>
@@ -6738,10 +6739,10 @@
       <c r="E5" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="2" t="s">
         <v>1919</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="2" t="s">
         <v>1920</v>
       </c>
     </row>
@@ -6761,10 +6762,10 @@
       <c r="E6" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="2" t="s">
         <v>1438</v>
       </c>
     </row>
@@ -6784,10 +6785,10 @@
       <c r="E7" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="2" t="s">
         <v>1451</v>
       </c>
     </row>
@@ -6807,10 +6808,10 @@
       <c r="E8" s="4" t="s">
         <v>1628</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="2" t="s">
         <v>1921</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="2" t="s">
         <v>1922</v>
       </c>
     </row>
@@ -6830,10 +6831,10 @@
       <c r="E9" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="2" t="s">
         <v>1923</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="2" t="s">
         <v>1924</v>
       </c>
     </row>
@@ -6853,10 +6854,10 @@
       <c r="E10" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="2" t="s">
         <v>1925</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="2" t="s">
         <v>1926</v>
       </c>
     </row>
@@ -6876,10 +6877,10 @@
       <c r="E11" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="2" t="s">
         <v>1927</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="2" t="s">
         <v>1928</v>
       </c>
     </row>
@@ -6899,10 +6900,10 @@
       <c r="E12" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="2" t="s">
         <v>1929</v>
       </c>
     </row>
@@ -6922,10 +6923,10 @@
       <c r="E13" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="2" t="s">
         <v>1930</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="2" t="s">
         <v>1931</v>
       </c>
     </row>
@@ -6945,10 +6946,10 @@
       <c r="E14" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="2" t="s">
         <v>1932</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="2" t="s">
         <v>1933</v>
       </c>
     </row>
@@ -6968,10 +6969,10 @@
       <c r="E15" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="2" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -6991,10 +6992,10 @@
       <c r="E16" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="2" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -7014,10 +7015,10 @@
       <c r="E17" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="2" t="s">
         <v>1934</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="2" t="s">
         <v>1935</v>
       </c>
     </row>
@@ -7037,10 +7038,10 @@
       <c r="E18" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="2" t="s">
         <v>1936</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="2" t="s">
         <v>1937</v>
       </c>
     </row>
@@ -7060,10 +7061,10 @@
       <c r="E19" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="2" t="s">
         <v>1938</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="2" t="s">
         <v>1939</v>
       </c>
     </row>
@@ -7083,10 +7084,10 @@
       <c r="E20" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="2" t="s">
         <v>1940</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="2" t="s">
         <v>1941</v>
       </c>
     </row>
@@ -7106,10 +7107,10 @@
       <c r="E21" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="2" t="s">
         <v>1942</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="2" t="s">
         <v>1943</v>
       </c>
     </row>
@@ -7129,10 +7130,10 @@
       <c r="E22" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="2" t="s">
         <v>1944</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="2" t="s">
         <v>1945</v>
       </c>
     </row>
@@ -7152,10 +7153,10 @@
       <c r="E23" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="2" t="s">
         <v>1360</v>
       </c>
     </row>
@@ -7175,10 +7176,10 @@
       <c r="E24" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="2" t="s">
         <v>1411</v>
       </c>
     </row>
@@ -7198,10 +7199,10 @@
       <c r="E25" s="4" t="s">
         <v>1676</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="2" t="s">
         <v>1414</v>
       </c>
     </row>
@@ -7221,10 +7222,10 @@
       <c r="E26" s="4" t="s">
         <v>1681</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="2" t="s">
         <v>1946</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="2" t="s">
         <v>1947</v>
       </c>
     </row>
@@ -7244,10 +7245,10 @@
       <c r="E27" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F27" s="5">
-        <v>912249226</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="F27" s="2" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>1435</v>
       </c>
     </row>
@@ -7267,10 +7268,10 @@
       <c r="E28" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="2" t="s">
         <v>1948</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="2" t="s">
         <v>1949</v>
       </c>
     </row>
@@ -7290,10 +7291,10 @@
       <c r="E29" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="2" t="s">
         <v>1375</v>
       </c>
     </row>
@@ -7313,10 +7314,10 @@
       <c r="E30" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="2" t="s">
         <v>1398</v>
       </c>
     </row>
@@ -7336,10 +7337,10 @@
       <c r="E31" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="2" t="s">
         <v>1950</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="2" t="s">
         <v>1951</v>
       </c>
     </row>
@@ -7359,10 +7360,10 @@
       <c r="E32" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="2" t="s">
         <v>1952</v>
       </c>
     </row>
@@ -7382,10 +7383,10 @@
       <c r="E33" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="2" t="s">
         <v>1953</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="2" t="s">
         <v>1954</v>
       </c>
     </row>
@@ -7405,10 +7406,10 @@
       <c r="E34" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="2" t="s">
         <v>1955</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="2" t="s">
         <v>1956</v>
       </c>
     </row>
@@ -7428,10 +7429,10 @@
       <c r="E35" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="2" t="s">
         <v>1381</v>
       </c>
     </row>
@@ -7451,10 +7452,10 @@
       <c r="E36" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="2" t="s">
         <v>1957</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="2" t="s">
         <v>1958</v>
       </c>
     </row>
@@ -7474,10 +7475,10 @@
       <c r="E37" s="4" t="s">
         <v>1711</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="2" t="s">
         <v>1959</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="2" t="s">
         <v>1959</v>
       </c>
     </row>
@@ -7497,10 +7498,10 @@
       <c r="E38" s="4" t="s">
         <v>1711</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="2" t="s">
         <v>1959</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="2" t="s">
         <v>1959</v>
       </c>
     </row>
@@ -7520,10 +7521,10 @@
       <c r="E39" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="2" t="s">
         <v>1960</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="2" t="s">
         <v>1961</v>
       </c>
     </row>
@@ -7543,10 +7544,10 @@
       <c r="E40" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="2" t="s">
         <v>1420</v>
       </c>
     </row>
@@ -7566,10 +7567,10 @@
       <c r="E41" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="2" t="s">
         <v>1343</v>
       </c>
     </row>
@@ -7589,10 +7590,10 @@
       <c r="E42" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="2" t="s">
         <v>1962</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="2" t="s">
         <v>1963</v>
       </c>
     </row>
@@ -7612,10 +7613,10 @@
       <c r="E43" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="2" t="s">
         <v>1520</v>
       </c>
     </row>
@@ -7635,10 +7636,10 @@
       <c r="E44" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="2" t="s">
         <v>1964</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="2" t="s">
         <v>1965</v>
       </c>
     </row>
@@ -7658,10 +7659,10 @@
       <c r="E45" s="4" t="s">
         <v>1735</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="2" t="s">
         <v>1966</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="2" t="s">
         <v>1967</v>
       </c>
     </row>
@@ -7681,10 +7682,10 @@
       <c r="E46" s="4" t="s">
         <v>1738</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="2" t="s">
         <v>1968</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="2" t="s">
         <v>1969</v>
       </c>
     </row>
@@ -7704,10 +7705,10 @@
       <c r="E47" s="4" t="s">
         <v>1741</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="2" t="s">
         <v>1970</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="2" t="s">
         <v>1100</v>
       </c>
     </row>
@@ -7727,10 +7728,10 @@
       <c r="E48" s="4" t="s">
         <v>1744</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="2" t="s">
         <v>1971</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="2" t="s">
         <v>1972</v>
       </c>
     </row>
@@ -7750,10 +7751,10 @@
       <c r="E49" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="2" t="s">
         <v>1973</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G49" s="2" t="s">
         <v>1974</v>
       </c>
     </row>
@@ -7773,10 +7774,10 @@
       <c r="E50" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="2" t="s">
         <v>1975</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="2" t="s">
         <v>1976</v>
       </c>
     </row>
@@ -7796,10 +7797,10 @@
       <c r="E51" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="2" t="s">
         <v>1977</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="G51" s="2" t="s">
         <v>1978</v>
       </c>
     </row>
@@ -7819,10 +7820,10 @@
       <c r="E52" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="2" t="s">
         <v>1979</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" s="2" t="s">
         <v>1980</v>
       </c>
     </row>
@@ -7842,10 +7843,10 @@
       <c r="E53" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="2" t="s">
         <v>1981</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G53" s="2" t="s">
         <v>1982</v>
       </c>
     </row>
@@ -7865,10 +7866,10 @@
       <c r="E54" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" s="2" t="s">
         <v>1369</v>
       </c>
     </row>
@@ -7888,10 +7889,10 @@
       <c r="E55" s="4" t="s">
         <v>1766</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="2" t="s">
         <v>1983</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="G55" s="2" t="s">
         <v>1984</v>
       </c>
     </row>
@@ -7911,10 +7912,10 @@
       <c r="E56" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="2" t="s">
         <v>1985</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="2" t="s">
         <v>1986</v>
       </c>
     </row>
@@ -7934,10 +7935,10 @@
       <c r="E57" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="2" t="s">
         <v>1987</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G57" s="2" t="s">
         <v>1988</v>
       </c>
     </row>
@@ -7957,10 +7958,10 @@
       <c r="E58" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="2" t="s">
         <v>1989</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="2" t="s">
         <v>1990</v>
       </c>
     </row>
@@ -7980,10 +7981,10 @@
       <c r="E59" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="2" t="s">
         <v>1991</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="G59" s="2" t="s">
         <v>1992</v>
       </c>
     </row>
@@ -8003,10 +8004,10 @@
       <c r="E60" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="2" t="s">
         <v>1497</v>
       </c>
     </row>
@@ -8026,10 +8027,10 @@
       <c r="E61" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="2" t="s">
         <v>1927</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="G61" s="2" t="s">
         <v>1928</v>
       </c>
     </row>
@@ -8049,10 +8050,10 @@
       <c r="E62" s="4" t="s">
         <v>1784</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="2" t="s">
         <v>1993</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="2" t="s">
         <v>1994</v>
       </c>
     </row>
@@ -8072,10 +8073,10 @@
       <c r="E63" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" s="2" t="s">
         <v>1523</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="2" t="s">
         <v>1995</v>
       </c>
     </row>
@@ -8095,10 +8096,10 @@
       <c r="E64" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="2" t="s">
         <v>1563</v>
       </c>
     </row>
@@ -8118,10 +8119,10 @@
       <c r="E65" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="2" t="s">
         <v>1996</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="G65" s="2" t="s">
         <v>1997</v>
       </c>
     </row>
@@ -8141,10 +8142,10 @@
       <c r="E66" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" s="2" t="s">
         <v>1444</v>
       </c>
     </row>
@@ -8164,10 +8165,10 @@
       <c r="E67" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="2" t="s">
         <v>1998</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="G67" s="2" t="s">
         <v>1999</v>
       </c>
     </row>
@@ -8187,10 +8188,10 @@
       <c r="E68" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="2" t="s">
         <v>2000</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G68" s="2" t="s">
         <v>2001</v>
       </c>
     </row>
@@ -8210,10 +8211,10 @@
       <c r="E69" s="4" t="s">
         <v>1744</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="2" t="s">
         <v>1971</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="2" t="s">
         <v>1972</v>
       </c>
     </row>
@@ -8233,10 +8234,10 @@
       <c r="E70" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="2" t="s">
         <v>1919</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="G70" s="2" t="s">
         <v>1920</v>
       </c>
     </row>
@@ -8256,10 +8257,10 @@
       <c r="E71" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="2" t="s">
         <v>2002</v>
       </c>
-      <c r="G71" s="5" t="s">
+      <c r="G71" s="2" t="s">
         <v>2003</v>
       </c>
     </row>
@@ -8279,10 +8280,10 @@
       <c r="E72" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="2" t="s">
         <v>2004</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="G72" s="2" t="s">
         <v>2005</v>
       </c>
     </row>
@@ -8302,10 +8303,10 @@
       <c r="E73" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="2" t="s">
         <v>2006</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="G73" s="2" t="s">
         <v>2006</v>
       </c>
     </row>
@@ -8325,10 +8326,10 @@
       <c r="E74" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="G74" s="2" t="s">
         <v>2007</v>
       </c>
     </row>
@@ -8348,10 +8349,10 @@
       <c r="E75" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="G75" s="5" t="s">
+      <c r="G75" s="2" t="s">
         <v>1445</v>
       </c>
     </row>
@@ -8371,10 +8372,10 @@
       <c r="E76" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="2" t="s">
         <v>2008</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G76" s="2" t="s">
         <v>2009</v>
       </c>
     </row>
@@ -8394,10 +8395,10 @@
       <c r="E77" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="2" t="s">
         <v>2010</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="G77" s="2" t="s">
         <v>2011</v>
       </c>
     </row>
@@ -8417,10 +8418,10 @@
       <c r="E78" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="2" t="s">
         <v>1989</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G78" s="2" t="s">
         <v>1990</v>
       </c>
     </row>
@@ -8440,10 +8441,10 @@
       <c r="E79" s="4" t="s">
         <v>1830</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="2" t="s">
         <v>2012</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="2" t="s">
         <v>2013</v>
       </c>
     </row>
@@ -8463,10 +8464,10 @@
       <c r="E80" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="F80" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="G80" s="2" t="s">
         <v>1415</v>
       </c>
     </row>
@@ -8486,10 +8487,10 @@
       <c r="E81" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F81" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="G81" s="2" t="s">
         <v>1460</v>
       </c>
     </row>
@@ -8509,10 +8510,10 @@
       <c r="E82" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F82" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="G82" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -8532,10 +8533,10 @@
       <c r="E83" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F83" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="G83" s="2" t="s">
         <v>1508</v>
       </c>
     </row>
@@ -8555,10 +8556,10 @@
       <c r="E84" s="4" t="s">
         <v>1845</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="2" t="s">
         <v>2014</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="G84" s="2" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -8578,10 +8579,10 @@
       <c r="E85" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F85" s="2" t="s">
         <v>2016</v>
       </c>
-      <c r="G85" s="5" t="s">
+      <c r="G85" s="2" t="s">
         <v>1364</v>
       </c>
     </row>
@@ -8601,10 +8602,10 @@
       <c r="E86" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="F86" s="2" t="s">
         <v>2017</v>
       </c>
-      <c r="G86" s="5" t="s">
+      <c r="G86" s="2" t="s">
         <v>2018</v>
       </c>
     </row>
@@ -8624,10 +8625,10 @@
       <c r="E87" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="2" t="s">
         <v>2019</v>
       </c>
-      <c r="G87" s="5" t="s">
+      <c r="G87" s="2" t="s">
         <v>2020</v>
       </c>
     </row>
@@ -8647,10 +8648,10 @@
       <c r="E88" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="F88" s="2" t="s">
         <v>2021</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="G88" s="2" t="s">
         <v>2022</v>
       </c>
     </row>
@@ -8670,10 +8671,10 @@
       <c r="E89" s="4" t="s">
         <v>1862</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F89" s="2" t="s">
         <v>2023</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="G89" s="2" t="s">
         <v>2024</v>
       </c>
     </row>
@@ -8693,10 +8694,10 @@
       <c r="E90" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="2" t="s">
         <v>2025</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="G90" s="2" t="s">
         <v>2026</v>
       </c>
     </row>
@@ -8716,10 +8717,10 @@
       <c r="E91" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="2" t="s">
         <v>2027</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G91" s="2" t="s">
         <v>2028</v>
       </c>
     </row>
@@ -8739,10 +8740,10 @@
       <c r="E92" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F92" s="2" t="s">
         <v>2029</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G92" s="2" t="s">
         <v>2030</v>
       </c>
     </row>
@@ -8762,10 +8763,10 @@
       <c r="E93" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F93" s="2" t="s">
         <v>2031</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G93" s="2" t="s">
         <v>2032</v>
       </c>
     </row>
@@ -8785,10 +8786,10 @@
       <c r="E94" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="2" t="s">
         <v>1495</v>
       </c>
     </row>
@@ -8808,10 +8809,10 @@
       <c r="E95" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" s="2" t="s">
         <v>2033</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="G95" s="2" t="s">
         <v>2034</v>
       </c>
     </row>
@@ -8831,10 +8832,10 @@
       <c r="E96" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="F96" s="2" t="s">
         <v>2035</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G96" s="2" t="s">
         <v>2036</v>
       </c>
     </row>
@@ -8854,10 +8855,10 @@
       <c r="E97" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F97" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="G97" s="2" t="s">
         <v>1345</v>
       </c>
     </row>
@@ -8877,10 +8878,10 @@
       <c r="E98" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F98" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="2" t="s">
         <v>1372</v>
       </c>
     </row>
@@ -8900,10 +8901,10 @@
       <c r="E99" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F99" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G99" s="2" t="s">
         <v>1395</v>
       </c>
     </row>
@@ -8923,10 +8924,10 @@
       <c r="E100" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F100" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="2" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -8946,10 +8947,10 @@
       <c r="E101" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F101" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G101" s="2" t="s">
         <v>1575</v>
       </c>
     </row>
@@ -8969,10 +8970,10 @@
       <c r="E102" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F102" s="2" t="s">
         <v>2037</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G102" s="2" t="s">
         <v>2038</v>
       </c>
     </row>
@@ -8992,10 +8993,10 @@
       <c r="E103" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F103" s="2" t="s">
         <v>1942</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G103" s="2" t="s">
         <v>1943</v>
       </c>
     </row>
@@ -9015,10 +9016,10 @@
       <c r="E104" s="4" t="s">
         <v>1905</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F104" s="2" t="s">
         <v>2039</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="2" t="s">
         <v>2040</v>
       </c>
     </row>
@@ -9038,10 +9039,10 @@
       <c r="E105" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="F105" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G105" s="2" t="s">
         <v>1373</v>
       </c>
     </row>
@@ -9061,10 +9062,10 @@
       <c r="E106" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="F106" s="2" t="s">
         <v>2041</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G106" s="2" t="s">
         <v>2042</v>
       </c>
     </row>
@@ -9084,10 +9085,10 @@
       <c r="E107" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="F107" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="G107" s="2" t="s">
         <v>1341</v>
       </c>
     </row>
@@ -9107,10 +9108,10 @@
       <c r="E108" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="F108" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="G108" s="2" t="s">
         <v>1342</v>
       </c>
     </row>
@@ -9130,10 +9131,10 @@
       <c r="E109" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="F109" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="G109" s="2" t="s">
         <v>1343</v>
       </c>
     </row>
@@ -9153,10 +9154,10 @@
       <c r="E110" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F110" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G110" s="2" t="s">
         <v>1344</v>
       </c>
     </row>
@@ -9176,10 +9177,10 @@
       <c r="E111" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="F111" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="G111" s="2" t="s">
         <v>1345</v>
       </c>
     </row>
@@ -9199,10 +9200,10 @@
       <c r="E112" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F112" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="G112" s="2" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -9222,10 +9223,10 @@
       <c r="E113" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="G113" s="2" t="s">
         <v>1347</v>
       </c>
     </row>
@@ -9245,10 +9246,10 @@
       <c r="E114" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F114" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G114" s="2" t="s">
         <v>1348</v>
       </c>
     </row>
@@ -9268,10 +9269,10 @@
       <c r="E115" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F115" s="5" t="s">
+      <c r="F115" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="G115" s="5" t="s">
+      <c r="G115" s="2" t="s">
         <v>1349</v>
       </c>
     </row>
@@ -9291,10 +9292,10 @@
       <c r="E116" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F116" s="5" t="s">
+      <c r="F116" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="G116" s="2" t="s">
         <v>1350</v>
       </c>
     </row>
@@ -9314,10 +9315,10 @@
       <c r="E117" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F117" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="G117" s="5" t="s">
+      <c r="G117" s="2" t="s">
         <v>1351</v>
       </c>
     </row>
@@ -9337,10 +9338,10 @@
       <c r="E118" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="G118" s="2" t="s">
         <v>1352</v>
       </c>
     </row>
@@ -9360,10 +9361,10 @@
       <c r="E119" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="F119" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="G119" s="2" t="s">
         <v>1353</v>
       </c>
     </row>
@@ -9383,10 +9384,10 @@
       <c r="E120" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="F120" s="5" t="s">
+      <c r="F120" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="G120" s="5" t="s">
+      <c r="G120" s="2" t="s">
         <v>1354</v>
       </c>
     </row>
@@ -9406,10 +9407,10 @@
       <c r="E121" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="F121" s="5" t="s">
+      <c r="F121" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="G121" s="5" t="s">
+      <c r="G121" s="2" t="s">
         <v>1355</v>
       </c>
     </row>
@@ -9429,10 +9430,10 @@
       <c r="E122" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F122" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="G122" s="5" t="s">
+      <c r="G122" s="2" t="s">
         <v>1356</v>
       </c>
     </row>
@@ -9452,10 +9453,10 @@
       <c r="E123" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F123" s="5" t="s">
+      <c r="F123" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="G123" s="5" t="s">
+      <c r="G123" s="2" t="s">
         <v>1357</v>
       </c>
     </row>
@@ -9475,10 +9476,10 @@
       <c r="E124" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="F124" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="G124" s="5" t="s">
+      <c r="G124" s="2" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -9498,10 +9499,10 @@
       <c r="E125" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F125" s="5" t="s">
+      <c r="F125" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="G125" s="5" t="s">
+      <c r="G125" s="2" t="s">
         <v>1359</v>
       </c>
     </row>
@@ -9521,10 +9522,10 @@
       <c r="E126" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F126" s="5" t="s">
+      <c r="F126" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="G126" s="5" t="s">
+      <c r="G126" s="2" t="s">
         <v>1360</v>
       </c>
     </row>
@@ -9544,10 +9545,10 @@
       <c r="E127" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="G127" s="5" t="s">
+      <c r="G127" s="2" t="s">
         <v>1361</v>
       </c>
     </row>
@@ -9567,10 +9568,10 @@
       <c r="E128" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F128" s="5" t="s">
+      <c r="F128" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="G128" s="5" t="s">
+      <c r="G128" s="2" t="s">
         <v>1362</v>
       </c>
     </row>
@@ -9590,10 +9591,10 @@
       <c r="E129" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F129" s="5" t="s">
+      <c r="F129" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="G129" s="5" t="s">
+      <c r="G129" s="2" t="s">
         <v>1363</v>
       </c>
     </row>
@@ -9613,10 +9614,10 @@
       <c r="E130" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="F130" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="G130" s="5" t="s">
+      <c r="G130" s="2" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -9636,10 +9637,10 @@
       <c r="E131" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F131" s="5" t="s">
+      <c r="F131" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="G131" s="5" t="s">
+      <c r="G131" s="2" t="s">
         <v>1364</v>
       </c>
     </row>
@@ -9659,10 +9660,10 @@
       <c r="E132" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F132" s="5" t="s">
+      <c r="F132" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="G132" s="5" t="s">
+      <c r="G132" s="2" t="s">
         <v>1365</v>
       </c>
     </row>
@@ -9682,10 +9683,10 @@
       <c r="E133" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F133" s="5" t="s">
+      <c r="F133" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="G133" s="5" t="s">
+      <c r="G133" s="2" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -9705,10 +9706,10 @@
       <c r="E134" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="F134" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="G134" s="5" t="s">
+      <c r="G134" s="2" t="s">
         <v>1367</v>
       </c>
     </row>
@@ -9728,10 +9729,10 @@
       <c r="E135" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F135" s="5" t="s">
+      <c r="F135" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="G135" s="5" t="s">
+      <c r="G135" s="2" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -9751,10 +9752,10 @@
       <c r="E136" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="F136" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="G136" s="5" t="s">
+      <c r="G136" s="2" t="s">
         <v>1369</v>
       </c>
     </row>
@@ -9774,10 +9775,10 @@
       <c r="E137" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="F137" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="G137" s="5" t="s">
+      <c r="G137" s="2" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -9797,10 +9798,10 @@
       <c r="E138" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="F138" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="G138" s="5" t="s">
+      <c r="G138" s="2" t="s">
         <v>1371</v>
       </c>
     </row>
@@ -9820,10 +9821,10 @@
       <c r="E139" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="F139" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="G139" s="5" t="s">
+      <c r="G139" s="2" t="s">
         <v>1372</v>
       </c>
     </row>
@@ -9843,10 +9844,10 @@
       <c r="E140" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="F140" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="G140" s="5" t="s">
+      <c r="G140" s="2" t="s">
         <v>1373</v>
       </c>
     </row>
@@ -9866,10 +9867,10 @@
       <c r="E141" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="F141" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G141" s="5" t="s">
+      <c r="G141" s="2" t="s">
         <v>1374</v>
       </c>
     </row>
@@ -9889,10 +9890,10 @@
       <c r="E142" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="F142" s="5" t="s">
+      <c r="F142" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="G142" s="5" t="s">
+      <c r="G142" s="2" t="s">
         <v>1375</v>
       </c>
     </row>
@@ -9912,10 +9913,10 @@
       <c r="E143" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F143" s="5" t="s">
+      <c r="F143" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="G143" s="5" t="s">
+      <c r="G143" s="2" t="s">
         <v>1376</v>
       </c>
     </row>
@@ -9935,10 +9936,10 @@
       <c r="E144" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="F144" s="5" t="s">
+      <c r="F144" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="G144" s="5" t="s">
+      <c r="G144" s="2" t="s">
         <v>1377</v>
       </c>
     </row>
@@ -9958,10 +9959,10 @@
       <c r="E145" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F145" s="5" t="s">
+      <c r="F145" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="G145" s="5" t="s">
+      <c r="G145" s="2" t="s">
         <v>1378</v>
       </c>
     </row>
@@ -9981,10 +9982,10 @@
       <c r="E146" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F146" s="5" t="s">
+      <c r="F146" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="G146" s="5" t="s">
+      <c r="G146" s="2" t="s">
         <v>1379</v>
       </c>
     </row>
@@ -10004,10 +10005,10 @@
       <c r="E147" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F147" s="5" t="s">
+      <c r="F147" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="G147" s="5" t="s">
+      <c r="G147" s="2" t="s">
         <v>1380</v>
       </c>
     </row>
@@ -10027,10 +10028,10 @@
       <c r="E148" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="F148" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="G148" s="2" t="s">
         <v>1381</v>
       </c>
     </row>
@@ -10050,10 +10051,10 @@
       <c r="E149" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F149" s="5" t="s">
+      <c r="F149" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="G149" s="5" t="s">
+      <c r="G149" s="2" t="s">
         <v>1382</v>
       </c>
     </row>
@@ -10073,10 +10074,10 @@
       <c r="E150" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F150" s="5" t="s">
+      <c r="F150" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="G150" s="5" t="s">
+      <c r="G150" s="2" t="s">
         <v>1383</v>
       </c>
     </row>
@@ -10096,10 +10097,10 @@
       <c r="E151" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F151" s="5" t="s">
+      <c r="F151" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="G151" s="5" t="s">
+      <c r="G151" s="2" t="s">
         <v>1384</v>
       </c>
     </row>
@@ -10119,10 +10120,10 @@
       <c r="E152" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="F152" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="G152" s="5" t="s">
+      <c r="G152" s="2" t="s">
         <v>1385</v>
       </c>
     </row>
@@ -10142,10 +10143,10 @@
       <c r="E153" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F153" s="5" t="s">
+      <c r="F153" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="G153" s="5" t="s">
+      <c r="G153" s="2" t="s">
         <v>1386</v>
       </c>
     </row>
@@ -10165,10 +10166,10 @@
       <c r="E154" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="F154" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="G154" s="5" t="s">
+      <c r="G154" s="2" t="s">
         <v>1387</v>
       </c>
     </row>
@@ -10188,10 +10189,10 @@
       <c r="E155" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F155" s="5" t="s">
+      <c r="F155" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="G155" s="5" t="s">
+      <c r="G155" s="2" t="s">
         <v>1388</v>
       </c>
     </row>
@@ -10211,10 +10212,10 @@
       <c r="E156" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="F156" s="5" t="s">
+      <c r="F156" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="G156" s="5" t="s">
+      <c r="G156" s="2" t="s">
         <v>1389</v>
       </c>
     </row>
@@ -10234,10 +10235,10 @@
       <c r="E157" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F157" s="5" t="s">
+      <c r="F157" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="G157" s="5" t="s">
+      <c r="G157" s="2" t="s">
         <v>1390</v>
       </c>
     </row>
@@ -10257,10 +10258,10 @@
       <c r="E158" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="G158" s="5" t="s">
+      <c r="G158" s="2" t="s">
         <v>1391</v>
       </c>
     </row>
@@ -10280,10 +10281,10 @@
       <c r="E159" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F159" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="G159" s="5" t="s">
+      <c r="G159" s="2" t="s">
         <v>1392</v>
       </c>
     </row>
@@ -10303,10 +10304,10 @@
       <c r="E160" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F160" s="5" t="s">
+      <c r="F160" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="G160" s="5" t="s">
+      <c r="G160" s="2" t="s">
         <v>1393</v>
       </c>
     </row>
@@ -10326,10 +10327,10 @@
       <c r="E161" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F161" s="5" t="s">
+      <c r="F161" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="G161" s="5" t="s">
+      <c r="G161" s="2" t="s">
         <v>1394</v>
       </c>
     </row>
@@ -10349,10 +10350,10 @@
       <c r="E162" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F162" s="5" t="s">
+      <c r="F162" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="G162" s="5" t="s">
+      <c r="G162" s="2" t="s">
         <v>1395</v>
       </c>
     </row>
@@ -10372,10 +10373,10 @@
       <c r="E163" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="F163" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="G163" s="5" t="s">
+      <c r="G163" s="2" t="s">
         <v>1396</v>
       </c>
     </row>
@@ -10395,10 +10396,10 @@
       <c r="E164" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F164" s="5" t="s">
+      <c r="F164" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="G164" s="5" t="s">
+      <c r="G164" s="2" t="s">
         <v>1397</v>
       </c>
     </row>
@@ -10418,10 +10419,10 @@
       <c r="E165" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="F165" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="G165" s="5" t="s">
+      <c r="G165" s="2" t="s">
         <v>1398</v>
       </c>
     </row>
@@ -10441,10 +10442,10 @@
       <c r="E166" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F166" s="5" t="s">
+      <c r="F166" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="G166" s="5" t="s">
+      <c r="G166" s="2" t="s">
         <v>1399</v>
       </c>
     </row>
@@ -10464,10 +10465,10 @@
       <c r="E167" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="F167" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="G167" s="5" t="s">
+      <c r="G167" s="2" t="s">
         <v>1400</v>
       </c>
     </row>
@@ -10487,10 +10488,10 @@
       <c r="E168" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F168" s="5" t="s">
+      <c r="F168" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="G168" s="5" t="s">
+      <c r="G168" s="2" t="s">
         <v>1401</v>
       </c>
     </row>
@@ -10510,10 +10511,10 @@
       <c r="E169" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="F169" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="G169" s="5" t="s">
+      <c r="G169" s="2" t="s">
         <v>1402</v>
       </c>
     </row>
@@ -10533,10 +10534,10 @@
       <c r="E170" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="F170" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="G170" s="5" t="s">
+      <c r="G170" s="2" t="s">
         <v>1403</v>
       </c>
     </row>
@@ -10556,10 +10557,10 @@
       <c r="E171" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="F171" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="G171" s="5" t="s">
+      <c r="G171" s="2" t="s">
         <v>1404</v>
       </c>
     </row>
@@ -10579,10 +10580,10 @@
       <c r="E172" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="F172" s="5" t="s">
+      <c r="F172" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="G172" s="5" t="s">
+      <c r="G172" s="2" t="s">
         <v>1405</v>
       </c>
     </row>
@@ -10602,10 +10603,10 @@
       <c r="E173" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F173" s="5" t="s">
+      <c r="F173" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="G173" s="5" t="s">
+      <c r="G173" s="2" t="s">
         <v>1406</v>
       </c>
     </row>
@@ -10625,10 +10626,10 @@
       <c r="E174" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F174" s="5" t="s">
+      <c r="F174" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="G174" s="5" t="s">
+      <c r="G174" s="2" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -10648,10 +10649,10 @@
       <c r="E175" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F175" s="5" t="s">
+      <c r="F175" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="G175" s="5" t="s">
+      <c r="G175" s="2" t="s">
         <v>1407</v>
       </c>
     </row>
@@ -10671,10 +10672,10 @@
       <c r="E176" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F176" s="5" t="s">
+      <c r="F176" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="G176" s="5" t="s">
+      <c r="G176" s="2" t="s">
         <v>1408</v>
       </c>
     </row>
@@ -10694,10 +10695,10 @@
       <c r="E177" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F177" s="5" t="s">
+      <c r="F177" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="G177" s="5" t="s">
+      <c r="G177" s="2" t="s">
         <v>1409</v>
       </c>
     </row>
@@ -10717,10 +10718,10 @@
       <c r="E178" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="F178" s="5" t="s">
+      <c r="F178" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="G178" s="5" t="s">
+      <c r="G178" s="2" t="s">
         <v>1410</v>
       </c>
     </row>
@@ -10740,10 +10741,10 @@
       <c r="E179" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F179" s="5" t="s">
+      <c r="F179" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="G179" s="5" t="s">
+      <c r="G179" s="2" t="s">
         <v>1411</v>
       </c>
     </row>
@@ -10763,10 +10764,10 @@
       <c r="E180" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="F180" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="G180" s="5" t="s">
+      <c r="G180" s="2" t="s">
         <v>1412</v>
       </c>
     </row>
@@ -10786,10 +10787,10 @@
       <c r="E181" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F181" s="5" t="s">
+      <c r="F181" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="G181" s="5" t="s">
+      <c r="G181" s="2" t="s">
         <v>1413</v>
       </c>
     </row>
@@ -10809,10 +10810,10 @@
       <c r="E182" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="G182" s="5" t="s">
+      <c r="G182" s="2" t="s">
         <v>1414</v>
       </c>
     </row>
@@ -10832,10 +10833,10 @@
       <c r="E183" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F183" s="5" t="s">
+      <c r="F183" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="G183" s="5" t="s">
+      <c r="G183" s="2" t="s">
         <v>1415</v>
       </c>
     </row>
@@ -10855,10 +10856,10 @@
       <c r="E184" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="F184" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="G184" s="5" t="s">
+      <c r="G184" s="2" t="s">
         <v>1416</v>
       </c>
     </row>
@@ -10878,10 +10879,10 @@
       <c r="E185" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F185" s="5" t="s">
+      <c r="F185" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="G185" s="5" t="s">
+      <c r="G185" s="2" t="s">
         <v>1417</v>
       </c>
     </row>
@@ -10901,10 +10902,10 @@
       <c r="E186" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="F186" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="G186" s="5" t="s">
+      <c r="G186" s="2" t="s">
         <v>1145</v>
       </c>
     </row>
@@ -10924,10 +10925,10 @@
       <c r="E187" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F187" s="5" t="s">
+      <c r="F187" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="G187" s="5" t="s">
+      <c r="G187" s="2" t="s">
         <v>1418</v>
       </c>
     </row>
@@ -10947,10 +10948,10 @@
       <c r="E188" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F188" s="5" t="s">
+      <c r="F188" s="2" t="s">
         <v>1147</v>
       </c>
-      <c r="G188" s="5" t="s">
+      <c r="G188" s="2" t="s">
         <v>1419</v>
       </c>
     </row>
@@ -10970,10 +10971,10 @@
       <c r="E189" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F189" s="5" t="s">
+      <c r="F189" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="G189" s="5" t="s">
+      <c r="G189" s="2" t="s">
         <v>1420</v>
       </c>
     </row>
@@ -10993,10 +10994,10 @@
       <c r="E190" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F190" s="5" t="s">
+      <c r="F190" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="G190" s="5" t="s">
+      <c r="G190" s="2" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -11016,10 +11017,10 @@
       <c r="E191" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F191" s="5" t="s">
+      <c r="F191" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="G191" s="5" t="s">
+      <c r="G191" s="2" t="s">
         <v>1422</v>
       </c>
     </row>
@@ -11039,10 +11040,10 @@
       <c r="E192" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F192" s="5" t="s">
+      <c r="F192" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="G192" s="5" t="s">
+      <c r="G192" s="2" t="s">
         <v>1423</v>
       </c>
     </row>
@@ -11062,10 +11063,10 @@
       <c r="E193" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F193" s="5" t="s">
+      <c r="F193" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="G193" s="5" t="s">
+      <c r="G193" s="2" t="s">
         <v>1424</v>
       </c>
     </row>
@@ -11085,10 +11086,10 @@
       <c r="E194" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F194" s="5" t="s">
+      <c r="F194" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="G194" s="5" t="s">
+      <c r="G194" s="2" t="s">
         <v>1425</v>
       </c>
     </row>
@@ -11108,10 +11109,10 @@
       <c r="E195" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F195" s="5" t="s">
+      <c r="F195" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="G195" s="5" t="s">
+      <c r="G195" s="2" t="s">
         <v>1426</v>
       </c>
     </row>
@@ -11131,10 +11132,10 @@
       <c r="E196" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="F196" s="5" t="s">
+      <c r="F196" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="G196" s="5" t="s">
+      <c r="G196" s="2" t="s">
         <v>1427</v>
       </c>
     </row>
@@ -11154,10 +11155,10 @@
       <c r="E197" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F197" s="5" t="s">
+      <c r="F197" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="G197" s="5" t="s">
+      <c r="G197" s="2" t="s">
         <v>1428</v>
       </c>
     </row>
@@ -11177,10 +11178,10 @@
       <c r="E198" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F198" s="5" t="s">
+      <c r="F198" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="G198" s="5" t="s">
+      <c r="G198" s="2" t="s">
         <v>1429</v>
       </c>
     </row>
@@ -11200,10 +11201,10 @@
       <c r="E199" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F199" s="5" t="s">
+      <c r="F199" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="G199" s="5" t="s">
+      <c r="G199" s="2" t="s">
         <v>1430</v>
       </c>
     </row>
@@ -11223,10 +11224,10 @@
       <c r="E200" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F200" s="5" t="s">
+      <c r="F200" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="G200" s="5" t="s">
+      <c r="G200" s="2" t="s">
         <v>1431</v>
       </c>
     </row>
@@ -11246,10 +11247,10 @@
       <c r="E201" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F201" s="5" t="s">
+      <c r="F201" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="G201" s="5" t="s">
+      <c r="G201" s="2" t="s">
         <v>1432</v>
       </c>
     </row>
@@ -11269,10 +11270,10 @@
       <c r="E202" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F202" s="5" t="s">
+      <c r="F202" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="G202" s="5" t="s">
+      <c r="G202" s="2" t="s">
         <v>1433</v>
       </c>
     </row>
@@ -11292,10 +11293,10 @@
       <c r="E203" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F203" s="5" t="s">
+      <c r="F203" s="2" t="s">
         <v>1162</v>
       </c>
-      <c r="G203" s="5" t="s">
+      <c r="G203" s="2" t="s">
         <v>1434</v>
       </c>
     </row>
@@ -11315,10 +11316,10 @@
       <c r="E204" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F204" s="5" t="s">
+      <c r="F204" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="G204" s="5" t="s">
+      <c r="G204" s="2" t="s">
         <v>1435</v>
       </c>
     </row>
@@ -11338,10 +11339,10 @@
       <c r="E205" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F205" s="5" t="s">
+      <c r="F205" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="G205" s="5" t="s">
+      <c r="G205" s="2" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -11361,10 +11362,10 @@
       <c r="E206" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F206" s="5" t="s">
+      <c r="F206" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="G206" s="5" t="s">
+      <c r="G206" s="2" t="s">
         <v>1437</v>
       </c>
     </row>
@@ -11384,10 +11385,10 @@
       <c r="E207" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F207" s="5" t="s">
+      <c r="F207" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="G207" s="5" t="s">
+      <c r="G207" s="2" t="s">
         <v>1438</v>
       </c>
     </row>
@@ -11407,10 +11408,10 @@
       <c r="E208" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F208" s="5" t="s">
+      <c r="F208" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="G208" s="5" t="s">
+      <c r="G208" s="2" t="s">
         <v>1439</v>
       </c>
     </row>
@@ -11430,10 +11431,10 @@
       <c r="E209" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F209" s="5" t="s">
+      <c r="F209" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="G209" s="5" t="s">
+      <c r="G209" s="2" t="s">
         <v>1440</v>
       </c>
     </row>
@@ -11453,10 +11454,10 @@
       <c r="E210" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F210" s="5" t="s">
+      <c r="F210" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="G210" s="5" t="s">
+      <c r="G210" s="2" t="s">
         <v>1441</v>
       </c>
     </row>
@@ -11476,10 +11477,10 @@
       <c r="E211" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F211" s="5" t="s">
+      <c r="F211" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="G211" s="5" t="s">
+      <c r="G211" s="2" t="s">
         <v>1442</v>
       </c>
     </row>
@@ -11499,10 +11500,10 @@
       <c r="E212" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F212" s="5" t="s">
+      <c r="F212" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="G212" s="5" t="s">
+      <c r="G212" s="2" t="s">
         <v>1397</v>
       </c>
     </row>
@@ -11522,10 +11523,10 @@
       <c r="E213" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F213" s="5" t="s">
+      <c r="F213" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="G213" s="5" t="s">
+      <c r="G213" s="2" t="s">
         <v>1443</v>
       </c>
     </row>
@@ -11545,10 +11546,10 @@
       <c r="E214" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F214" s="5" t="s">
+      <c r="F214" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="G214" s="5" t="s">
+      <c r="G214" s="2" t="s">
         <v>1444</v>
       </c>
     </row>
@@ -11568,10 +11569,10 @@
       <c r="E215" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F215" s="5" t="s">
+      <c r="F215" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="G215" s="5" t="s">
+      <c r="G215" s="2" t="s">
         <v>1445</v>
       </c>
     </row>
@@ -11591,10 +11592,10 @@
       <c r="E216" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F216" s="5" t="s">
+      <c r="F216" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="G216" s="5" t="s">
+      <c r="G216" s="2" t="s">
         <v>1446</v>
       </c>
     </row>
@@ -11614,10 +11615,10 @@
       <c r="E217" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F217" s="5" t="s">
+      <c r="F217" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="G217" s="5" t="s">
+      <c r="G217" s="2" t="s">
         <v>1447</v>
       </c>
     </row>
@@ -11637,10 +11638,10 @@
       <c r="E218" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F218" s="5" t="s">
+      <c r="F218" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="G218" s="5" t="s">
+      <c r="G218" s="2" t="s">
         <v>1448</v>
       </c>
     </row>
@@ -11660,10 +11661,10 @@
       <c r="E219" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F219" s="5" t="s">
+      <c r="F219" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="G219" s="5" t="s">
+      <c r="G219" s="2" t="s">
         <v>1449</v>
       </c>
     </row>
@@ -11683,10 +11684,10 @@
       <c r="E220" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F220" s="5" t="s">
+      <c r="F220" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="G220" s="5" t="s">
+      <c r="G220" s="2" t="s">
         <v>1391</v>
       </c>
     </row>
@@ -11706,10 +11707,10 @@
       <c r="E221" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F221" s="5" t="s">
+      <c r="F221" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="G221" s="5" t="s">
+      <c r="G221" s="2" t="s">
         <v>1450</v>
       </c>
     </row>
@@ -11729,10 +11730,10 @@
       <c r="E222" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F222" s="5" t="s">
+      <c r="F222" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="G222" s="5" t="s">
+      <c r="G222" s="2" t="s">
         <v>1451</v>
       </c>
     </row>
@@ -11752,10 +11753,10 @@
       <c r="E223" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F223" s="5" t="s">
+      <c r="F223" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="G223" s="5" t="s">
+      <c r="G223" s="2" t="s">
         <v>1452</v>
       </c>
     </row>
@@ -11775,10 +11776,10 @@
       <c r="E224" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F224" s="5" t="s">
+      <c r="F224" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="G224" s="5" t="s">
+      <c r="G224" s="2" t="s">
         <v>1453</v>
       </c>
     </row>
@@ -11798,10 +11799,10 @@
       <c r="E225" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F225" s="5" t="s">
+      <c r="F225" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="G225" s="5" t="s">
+      <c r="G225" s="2" t="s">
         <v>1454</v>
       </c>
     </row>
@@ -11821,10 +11822,10 @@
       <c r="E226" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F226" s="5" t="s">
+      <c r="F226" s="2" t="s">
         <v>1183</v>
       </c>
-      <c r="G226" s="5" t="s">
+      <c r="G226" s="2" t="s">
         <v>1455</v>
       </c>
     </row>
@@ -11844,10 +11845,10 @@
       <c r="E227" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F227" s="5" t="s">
+      <c r="F227" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="G227" s="5" t="s">
+      <c r="G227" s="2" t="s">
         <v>1184</v>
       </c>
     </row>
@@ -11867,10 +11868,10 @@
       <c r="E228" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F228" s="5" t="s">
+      <c r="F228" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="G228" s="2" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -11890,10 +11891,10 @@
       <c r="E229" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F229" s="5" t="s">
+      <c r="F229" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="G229" s="5" t="s">
+      <c r="G229" s="2" t="s">
         <v>1457</v>
       </c>
     </row>
@@ -11913,10 +11914,10 @@
       <c r="E230" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F230" s="5" t="s">
+      <c r="F230" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="G230" s="5" t="s">
+      <c r="G230" s="2" t="s">
         <v>1187</v>
       </c>
     </row>
@@ -11936,10 +11937,10 @@
       <c r="E231" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F231" s="5" t="s">
+      <c r="F231" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="G231" s="5" t="s">
+      <c r="G231" s="2" t="s">
         <v>1187</v>
       </c>
     </row>
@@ -11959,10 +11960,10 @@
       <c r="E232" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F232" s="5" t="s">
+      <c r="F232" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="G232" s="5" t="s">
+      <c r="G232" s="2" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -11982,10 +11983,10 @@
       <c r="E233" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F233" s="5" t="s">
+      <c r="F233" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="G233" s="5" t="s">
+      <c r="G233" s="2" t="s">
         <v>1459</v>
       </c>
     </row>
@@ -12005,10 +12006,10 @@
       <c r="E234" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F234" s="5" t="s">
+      <c r="F234" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="G234" s="5" t="s">
+      <c r="G234" s="2" t="s">
         <v>1460</v>
       </c>
     </row>
@@ -12028,10 +12029,10 @@
       <c r="E235" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F235" s="5" t="s">
+      <c r="F235" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="G235" s="5" t="s">
+      <c r="G235" s="2" t="s">
         <v>1461</v>
       </c>
     </row>
@@ -12051,10 +12052,10 @@
       <c r="E236" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F236" s="5" t="s">
+      <c r="F236" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="G236" s="5" t="s">
+      <c r="G236" s="2" t="s">
         <v>1462</v>
       </c>
     </row>
@@ -12074,10 +12075,10 @@
       <c r="E237" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F237" s="5" t="s">
+      <c r="F237" s="2" t="s">
         <v>1193</v>
       </c>
-      <c r="G237" s="5" t="s">
+      <c r="G237" s="2" t="s">
         <v>1463</v>
       </c>
     </row>
@@ -12097,10 +12098,10 @@
       <c r="E238" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F238" s="5" t="s">
+      <c r="F238" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="G238" s="5" t="s">
+      <c r="G238" s="2" t="s">
         <v>1464</v>
       </c>
     </row>
@@ -12120,10 +12121,10 @@
       <c r="E239" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F239" s="5" t="s">
+      <c r="F239" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="G239" s="5" t="s">
+      <c r="G239" s="2" t="s">
         <v>1465</v>
       </c>
     </row>
@@ -12143,10 +12144,10 @@
       <c r="E240" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F240" s="5" t="s">
+      <c r="F240" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="G240" s="5" t="s">
+      <c r="G240" s="2" t="s">
         <v>1466</v>
       </c>
     </row>
@@ -12166,10 +12167,10 @@
       <c r="E241" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F241" s="5" t="s">
+      <c r="F241" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="G241" s="5" t="s">
+      <c r="G241" s="2" t="s">
         <v>1461</v>
       </c>
     </row>
@@ -12189,10 +12190,10 @@
       <c r="E242" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F242" s="5" t="s">
+      <c r="F242" s="2" t="s">
         <v>1197</v>
       </c>
-      <c r="G242" s="5" t="s">
+      <c r="G242" s="2" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -12212,10 +12213,10 @@
       <c r="E243" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F243" s="5" t="s">
+      <c r="F243" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="G243" s="5" t="s">
+      <c r="G243" s="2" t="s">
         <v>1468</v>
       </c>
     </row>
@@ -12235,10 +12236,10 @@
       <c r="E244" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F244" s="5" t="s">
+      <c r="F244" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="G244" s="5" t="s">
+      <c r="G244" s="2" t="s">
         <v>1469</v>
       </c>
     </row>
@@ -12258,10 +12259,10 @@
       <c r="E245" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F245" s="5" t="s">
+      <c r="F245" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="G245" s="5" t="s">
+      <c r="G245" s="2" t="s">
         <v>1470</v>
       </c>
     </row>
@@ -12281,10 +12282,10 @@
       <c r="E246" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F246" s="5" t="s">
+      <c r="F246" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="G246" s="5" t="s">
+      <c r="G246" s="2" t="s">
         <v>1408</v>
       </c>
     </row>
@@ -12304,10 +12305,10 @@
       <c r="E247" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="F247" s="5" t="s">
+      <c r="F247" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="G247" s="5" t="s">
+      <c r="G247" s="2" t="s">
         <v>1100</v>
       </c>
     </row>
@@ -12327,10 +12328,10 @@
       <c r="E248" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F248" s="5" t="s">
+      <c r="F248" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="G248" s="5" t="s">
+      <c r="G248" s="2" t="s">
         <v>1471</v>
       </c>
     </row>
@@ -12350,10 +12351,10 @@
       <c r="E249" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="F249" s="5" t="s">
+      <c r="F249" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="G249" s="5" t="s">
+      <c r="G249" s="2" t="s">
         <v>1472</v>
       </c>
     </row>
@@ -12373,10 +12374,10 @@
       <c r="E250" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F250" s="5" t="s">
+      <c r="F250" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="G250" s="5" t="s">
+      <c r="G250" s="2" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -12396,10 +12397,10 @@
       <c r="E251" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F251" s="5" t="s">
+      <c r="F251" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="G251" s="5" t="s">
+      <c r="G251" s="2" t="s">
         <v>1474</v>
       </c>
     </row>
@@ -12419,10 +12420,10 @@
       <c r="E252" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F252" s="5" t="s">
+      <c r="F252" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="G252" s="5" t="s">
+      <c r="G252" s="2" t="s">
         <v>1475</v>
       </c>
     </row>
@@ -12442,10 +12443,10 @@
       <c r="E253" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F253" s="5" t="s">
+      <c r="F253" s="2" t="s">
         <v>1207</v>
       </c>
-      <c r="G253" s="5" t="s">
+      <c r="G253" s="2" t="s">
         <v>1476</v>
       </c>
     </row>
@@ -12465,10 +12466,10 @@
       <c r="E254" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F254" s="5" t="s">
+      <c r="F254" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="G254" s="5" t="s">
+      <c r="G254" s="2" t="s">
         <v>1407</v>
       </c>
     </row>
@@ -12488,10 +12489,10 @@
       <c r="E255" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F255" s="5" t="s">
+      <c r="F255" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="G255" s="5" t="s">
+      <c r="G255" s="2" t="s">
         <v>1477</v>
       </c>
     </row>
@@ -12511,10 +12512,10 @@
       <c r="E256" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F256" s="5" t="s">
+      <c r="F256" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="G256" s="5" t="s">
+      <c r="G256" s="2" t="s">
         <v>1478</v>
       </c>
     </row>
@@ -12534,10 +12535,10 @@
       <c r="E257" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F257" s="5" t="s">
+      <c r="F257" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="G257" s="5" t="s">
+      <c r="G257" s="2" t="s">
         <v>1479</v>
       </c>
     </row>
@@ -12557,10 +12558,10 @@
       <c r="E258" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F258" s="5" t="s">
+      <c r="F258" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="G258" s="5" t="s">
+      <c r="G258" s="2" t="s">
         <v>1480</v>
       </c>
     </row>
@@ -12580,10 +12581,10 @@
       <c r="E259" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F259" s="5" t="s">
+      <c r="F259" s="2" t="s">
         <v>1212</v>
       </c>
-      <c r="G259" s="5" t="s">
+      <c r="G259" s="2" t="s">
         <v>1481</v>
       </c>
     </row>
@@ -12603,10 +12604,10 @@
       <c r="E260" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F260" s="5" t="s">
+      <c r="F260" s="2" t="s">
         <v>1213</v>
       </c>
-      <c r="G260" s="5" t="s">
+      <c r="G260" s="2" t="s">
         <v>1482</v>
       </c>
     </row>
@@ -12626,10 +12627,10 @@
       <c r="E261" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F261" s="5" t="s">
+      <c r="F261" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="G261" s="5" t="s">
+      <c r="G261" s="2" t="s">
         <v>1483</v>
       </c>
     </row>
@@ -12649,10 +12650,10 @@
       <c r="E262" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F262" s="5" t="s">
+      <c r="F262" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="G262" s="5" t="s">
+      <c r="G262" s="2" t="s">
         <v>1484</v>
       </c>
     </row>
@@ -12672,10 +12673,10 @@
       <c r="E263" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F263" s="5" t="s">
+      <c r="F263" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="G263" s="5" t="s">
+      <c r="G263" s="2" t="s">
         <v>1485</v>
       </c>
     </row>
@@ -12695,10 +12696,10 @@
       <c r="E264" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F264" s="5" t="s">
+      <c r="F264" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="G264" s="5" t="s">
+      <c r="G264" s="2" t="s">
         <v>1486</v>
       </c>
     </row>
@@ -12718,10 +12719,10 @@
       <c r="E265" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F265" s="5" t="s">
+      <c r="F265" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="G265" s="5" t="s">
+      <c r="G265" s="2" t="s">
         <v>1487</v>
       </c>
     </row>
@@ -12741,10 +12742,10 @@
       <c r="E266" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F266" s="5" t="s">
+      <c r="F266" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="G266" s="5" t="s">
+      <c r="G266" s="2" t="s">
         <v>1488</v>
       </c>
     </row>
@@ -12764,10 +12765,10 @@
       <c r="E267" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F267" s="5" t="s">
+      <c r="F267" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="G267" s="5" t="s">
+      <c r="G267" s="2" t="s">
         <v>1489</v>
       </c>
     </row>
@@ -12787,10 +12788,10 @@
       <c r="E268" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F268" s="5" t="s">
+      <c r="F268" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="G268" s="5" t="s">
+      <c r="G268" s="2" t="s">
         <v>1490</v>
       </c>
     </row>
@@ -12810,10 +12811,10 @@
       <c r="E269" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F269" s="5" t="s">
+      <c r="F269" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="G269" s="5" t="s">
+      <c r="G269" s="2" t="s">
         <v>1491</v>
       </c>
     </row>
@@ -12833,10 +12834,10 @@
       <c r="E270" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F270" s="5" t="s">
+      <c r="F270" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="G270" s="5" t="s">
+      <c r="G270" s="2" t="s">
         <v>1492</v>
       </c>
     </row>
@@ -12856,10 +12857,10 @@
       <c r="E271" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F271" s="5" t="s">
+      <c r="F271" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="G271" s="5" t="s">
+      <c r="G271" s="2" t="s">
         <v>1493</v>
       </c>
     </row>
@@ -12879,10 +12880,10 @@
       <c r="E272" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F272" s="5" t="s">
+      <c r="F272" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="G272" s="5" t="s">
+      <c r="G272" s="2" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -12902,10 +12903,10 @@
       <c r="E273" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F273" s="5" t="s">
+      <c r="F273" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="G273" s="5" t="s">
+      <c r="G273" s="2" t="s">
         <v>1495</v>
       </c>
     </row>
@@ -12925,10 +12926,10 @@
       <c r="E274" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F274" s="5" t="s">
+      <c r="F274" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="G274" s="5" t="s">
+      <c r="G274" s="2" t="s">
         <v>1496</v>
       </c>
     </row>
@@ -12948,10 +12949,10 @@
       <c r="E275" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F275" s="5" t="s">
+      <c r="F275" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="G275" s="5" t="s">
+      <c r="G275" s="2" t="s">
         <v>1497</v>
       </c>
     </row>
@@ -12971,10 +12972,10 @@
       <c r="E276" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="F276" s="5" t="s">
+      <c r="F276" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="G276" s="5" t="s">
+      <c r="G276" s="2" t="s">
         <v>1498</v>
       </c>
     </row>
@@ -12994,10 +12995,10 @@
       <c r="E277" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="F277" s="5" t="s">
+      <c r="F277" s="2" t="s">
         <v>1230</v>
       </c>
-      <c r="G277" s="5" t="s">
+      <c r="G277" s="2" t="s">
         <v>1499</v>
       </c>
     </row>
@@ -13017,10 +13018,10 @@
       <c r="E278" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F278" s="5" t="s">
+      <c r="F278" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="G278" s="5" t="s">
+      <c r="G278" s="2" t="s">
         <v>1400</v>
       </c>
     </row>
@@ -13040,10 +13041,10 @@
       <c r="E279" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="F279" s="5" t="s">
+      <c r="F279" s="2" t="s">
         <v>1231</v>
       </c>
-      <c r="G279" s="5" t="s">
+      <c r="G279" s="2" t="s">
         <v>1500</v>
       </c>
     </row>
@@ -13063,10 +13064,10 @@
       <c r="E280" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F280" s="5" t="s">
+      <c r="F280" s="2" t="s">
         <v>1232</v>
       </c>
-      <c r="G280" s="5" t="s">
+      <c r="G280" s="2" t="s">
         <v>1501</v>
       </c>
     </row>
@@ -13086,10 +13087,10 @@
       <c r="E281" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F281" s="5" t="s">
+      <c r="F281" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="G281" s="5" t="s">
+      <c r="G281" s="2" t="s">
         <v>1502</v>
       </c>
     </row>
@@ -13109,10 +13110,10 @@
       <c r="E282" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F282" s="5" t="s">
+      <c r="F282" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="G282" s="5" t="s">
+      <c r="G282" s="2" t="s">
         <v>1503</v>
       </c>
     </row>
@@ -13132,10 +13133,10 @@
       <c r="E283" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F283" s="5" t="s">
+      <c r="F283" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="G283" s="5" t="s">
+      <c r="G283" s="2" t="s">
         <v>1504</v>
       </c>
     </row>
@@ -13155,10 +13156,10 @@
       <c r="E284" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F284" s="5" t="s">
+      <c r="F284" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="G284" s="5" t="s">
+      <c r="G284" s="2" t="s">
         <v>1505</v>
       </c>
     </row>
@@ -13178,10 +13179,10 @@
       <c r="E285" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F285" s="5" t="s">
+      <c r="F285" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="G285" s="5" t="s">
+      <c r="G285" s="2" t="s">
         <v>1506</v>
       </c>
     </row>
@@ -13201,10 +13202,10 @@
       <c r="E286" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F286" s="5" t="s">
+      <c r="F286" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="G286" s="5" t="s">
+      <c r="G286" s="2" t="s">
         <v>1507</v>
       </c>
     </row>
@@ -13224,10 +13225,10 @@
       <c r="E287" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F287" s="5" t="s">
+      <c r="F287" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="G287" s="5" t="s">
+      <c r="G287" s="2" t="s">
         <v>1508</v>
       </c>
     </row>
@@ -13247,10 +13248,10 @@
       <c r="E288" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="F288" s="5" t="s">
+      <c r="F288" s="2" t="s">
         <v>1155</v>
       </c>
-      <c r="G288" s="5" t="s">
+      <c r="G288" s="2" t="s">
         <v>1427</v>
       </c>
     </row>
@@ -13270,10 +13271,10 @@
       <c r="E289" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F289" s="5" t="s">
+      <c r="F289" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="G289" s="5" t="s">
+      <c r="G289" s="2" t="s">
         <v>1509</v>
       </c>
     </row>
@@ -13293,10 +13294,10 @@
       <c r="E290" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F290" s="5" t="s">
+      <c r="F290" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="G290" s="5" t="s">
+      <c r="G290" s="2" t="s">
         <v>1510</v>
       </c>
     </row>
@@ -13316,10 +13317,10 @@
       <c r="E291" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F291" s="5" t="s">
+      <c r="F291" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="G291" s="5" t="s">
+      <c r="G291" s="2" t="s">
         <v>1511</v>
       </c>
     </row>
@@ -13339,10 +13340,10 @@
       <c r="E292" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F292" s="5" t="s">
+      <c r="F292" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="G292" s="5" t="s">
+      <c r="G292" s="2" t="s">
         <v>1512</v>
       </c>
     </row>
@@ -13362,10 +13363,10 @@
       <c r="E293" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F293" s="5" t="s">
+      <c r="F293" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="G293" s="5" t="s">
+      <c r="G293" s="2" t="s">
         <v>1513</v>
       </c>
     </row>
@@ -13385,10 +13386,10 @@
       <c r="E294" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F294" s="5" t="s">
+      <c r="F294" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G294" s="5" t="s">
+      <c r="G294" s="2" t="s">
         <v>1514</v>
       </c>
     </row>
@@ -13408,10 +13409,10 @@
       <c r="E295" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F295" s="5" t="s">
+      <c r="F295" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="G295" s="5" t="s">
+      <c r="G295" s="2" t="s">
         <v>1515</v>
       </c>
     </row>
@@ -13431,10 +13432,10 @@
       <c r="E296" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F296" s="5" t="s">
+      <c r="F296" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="G296" s="5" t="s">
+      <c r="G296" s="2" t="s">
         <v>1516</v>
       </c>
     </row>
@@ -13454,10 +13455,10 @@
       <c r="E297" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F297" s="5" t="s">
+      <c r="F297" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="G297" s="5" t="s">
+      <c r="G297" s="2" t="s">
         <v>1485</v>
       </c>
     </row>
@@ -13477,10 +13478,10 @@
       <c r="E298" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="F298" s="5" t="s">
+      <c r="F298" s="2" t="s">
         <v>1247</v>
       </c>
-      <c r="G298" s="5" t="s">
+      <c r="G298" s="2" t="s">
         <v>1517</v>
       </c>
     </row>
@@ -13500,10 +13501,10 @@
       <c r="E299" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F299" s="5" t="s">
+      <c r="F299" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="G299" s="5" t="s">
+      <c r="G299" s="2" t="s">
         <v>1518</v>
       </c>
     </row>
@@ -13523,10 +13524,10 @@
       <c r="E300" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F300" s="5" t="s">
+      <c r="F300" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="G300" s="5" t="s">
+      <c r="G300" s="2" t="s">
         <v>1459</v>
       </c>
     </row>
@@ -13546,10 +13547,10 @@
       <c r="E301" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F301" s="5" t="s">
+      <c r="F301" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="G301" s="5" t="s">
+      <c r="G301" s="2" t="s">
         <v>1519</v>
       </c>
     </row>
@@ -13569,10 +13570,10 @@
       <c r="E302" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F302" s="5" t="s">
+      <c r="F302" s="2" t="s">
         <v>1250</v>
       </c>
-      <c r="G302" s="5" t="s">
+      <c r="G302" s="2" t="s">
         <v>1145</v>
       </c>
     </row>
@@ -13592,10 +13593,10 @@
       <c r="E303" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F303" s="5" t="s">
+      <c r="F303" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="G303" s="5" t="s">
+      <c r="G303" s="2" t="s">
         <v>1508</v>
       </c>
     </row>
@@ -13615,10 +13616,10 @@
       <c r="E304" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F304" s="5" t="s">
+      <c r="F304" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="G304" s="5" t="s">
+      <c r="G304" s="2" t="s">
         <v>1520</v>
       </c>
     </row>
@@ -13638,10 +13639,10 @@
       <c r="E305" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F305" s="5" t="s">
+      <c r="F305" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="G305" s="5" t="s">
+      <c r="G305" s="2" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -13661,10 +13662,10 @@
       <c r="E306" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F306" s="5" t="s">
+      <c r="F306" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="G306" s="5" t="s">
+      <c r="G306" s="2" t="s">
         <v>1521</v>
       </c>
     </row>
@@ -13684,10 +13685,10 @@
       <c r="E307" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F307" s="5" t="s">
+      <c r="F307" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="G307" s="5" t="s">
+      <c r="G307" s="2" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -13707,10 +13708,10 @@
       <c r="E308" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F308" s="5" t="s">
+      <c r="F308" s="2" t="s">
         <v>1254</v>
       </c>
-      <c r="G308" s="5" t="s">
+      <c r="G308" s="2" t="s">
         <v>1522</v>
       </c>
     </row>
@@ -13730,10 +13731,10 @@
       <c r="E309" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="F309" s="5" t="s">
+      <c r="F309" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="G309" s="5" t="s">
+      <c r="G309" s="2" t="s">
         <v>1523</v>
       </c>
     </row>
@@ -13753,10 +13754,10 @@
       <c r="E310" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F310" s="5" t="s">
+      <c r="F310" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="G310" s="5" t="s">
+      <c r="G310" s="2" t="s">
         <v>1524</v>
       </c>
     </row>
@@ -13776,10 +13777,10 @@
       <c r="E311" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F311" s="5" t="s">
+      <c r="F311" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="G311" s="5" t="s">
+      <c r="G311" s="2" t="s">
         <v>1525</v>
       </c>
     </row>
@@ -13799,10 +13800,10 @@
       <c r="E312" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F312" s="5" t="s">
+      <c r="F312" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="G312" s="5" t="s">
+      <c r="G312" s="2" t="s">
         <v>1526</v>
       </c>
     </row>
@@ -13822,10 +13823,10 @@
       <c r="E313" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F313" s="5" t="s">
+      <c r="F313" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="G313" s="5" t="s">
+      <c r="G313" s="2" t="s">
         <v>1527</v>
       </c>
     </row>
@@ -13845,10 +13846,10 @@
       <c r="E314" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F314" s="5" t="s">
+      <c r="F314" s="2" t="s">
         <v>1259</v>
       </c>
-      <c r="G314" s="5" t="s">
+      <c r="G314" s="2" t="s">
         <v>1528</v>
       </c>
     </row>
@@ -13868,10 +13869,10 @@
       <c r="E315" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F315" s="5" t="s">
+      <c r="F315" s="2" t="s">
         <v>1260</v>
       </c>
-      <c r="G315" s="5" t="s">
+      <c r="G315" s="2" t="s">
         <v>1529</v>
       </c>
     </row>
@@ -13891,10 +13892,10 @@
       <c r="E316" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F316" s="5" t="s">
+      <c r="F316" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="G316" s="5" t="s">
+      <c r="G316" s="2" t="s">
         <v>1441</v>
       </c>
     </row>
@@ -13914,10 +13915,10 @@
       <c r="E317" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="F317" s="5" t="s">
+      <c r="F317" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="G317" s="5" t="s">
+      <c r="G317" s="2" t="s">
         <v>1405</v>
       </c>
     </row>
@@ -13937,10 +13938,10 @@
       <c r="E318" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F318" s="5" t="s">
+      <c r="F318" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="G318" s="5" t="s">
+      <c r="G318" s="2" t="s">
         <v>1530</v>
       </c>
     </row>
@@ -13960,10 +13961,10 @@
       <c r="E319" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F319" s="5" t="s">
+      <c r="F319" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="G319" s="5" t="s">
+      <c r="G319" s="2" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -13983,10 +13984,10 @@
       <c r="E320" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F320" s="5" t="s">
+      <c r="F320" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="G320" s="5" t="s">
+      <c r="G320" s="2" t="s">
         <v>1401</v>
       </c>
     </row>
@@ -14006,10 +14007,10 @@
       <c r="E321" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F321" s="5" t="s">
+      <c r="F321" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="G321" s="5" t="s">
+      <c r="G321" s="2" t="s">
         <v>1428</v>
       </c>
     </row>
@@ -14029,10 +14030,10 @@
       <c r="E322" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F322" s="5" t="s">
+      <c r="F322" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="G322" s="5" t="s">
+      <c r="G322" s="2" t="s">
         <v>1430</v>
       </c>
     </row>
@@ -14052,10 +14053,10 @@
       <c r="E323" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F323" s="5" t="s">
+      <c r="F323" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="G323" s="5" t="s">
+      <c r="G323" s="2" t="s">
         <v>1531</v>
       </c>
     </row>
@@ -14075,10 +14076,10 @@
       <c r="E324" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="F324" s="5" t="s">
+      <c r="F324" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="G324" s="5" t="s">
+      <c r="G324" s="2" t="s">
         <v>1472</v>
       </c>
     </row>
@@ -14098,10 +14099,10 @@
       <c r="E325" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F325" s="5" t="s">
+      <c r="F325" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="G325" s="5" t="s">
+      <c r="G325" s="2" t="s">
         <v>1532</v>
       </c>
     </row>
@@ -14121,10 +14122,10 @@
       <c r="E326" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F326" s="5" t="s">
+      <c r="F326" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="G326" s="5" t="s">
+      <c r="G326" s="2" t="s">
         <v>1450</v>
       </c>
     </row>
@@ -14144,10 +14145,10 @@
       <c r="E327" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F327" s="5" t="s">
+      <c r="F327" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="G327" s="5" t="s">
+      <c r="G327" s="2" t="s">
         <v>1533</v>
       </c>
     </row>
@@ -14167,10 +14168,10 @@
       <c r="E328" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F328" s="5" t="s">
+      <c r="F328" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="G328" s="5" t="s">
+      <c r="G328" s="2" t="s">
         <v>1265</v>
       </c>
     </row>
@@ -14190,10 +14191,10 @@
       <c r="E329" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F329" s="5" t="s">
+      <c r="F329" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="G329" s="5" t="s">
+      <c r="G329" s="2" t="s">
         <v>1534</v>
       </c>
     </row>
@@ -14213,10 +14214,10 @@
       <c r="E330" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F330" s="5" t="s">
+      <c r="F330" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="G330" s="5" t="s">
+      <c r="G330" s="2" t="s">
         <v>1535</v>
       </c>
     </row>
@@ -14236,10 +14237,10 @@
       <c r="E331" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F331" s="5" t="s">
+      <c r="F331" s="2" t="s">
         <v>1268</v>
       </c>
-      <c r="G331" s="5" t="s">
+      <c r="G331" s="2" t="s">
         <v>1536</v>
       </c>
     </row>
@@ -14259,10 +14260,10 @@
       <c r="E332" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F332" s="5" t="s">
+      <c r="F332" s="2" t="s">
         <v>1269</v>
       </c>
-      <c r="G332" s="5" t="s">
+      <c r="G332" s="2" t="s">
         <v>1537</v>
       </c>
     </row>
@@ -14282,10 +14283,10 @@
       <c r="E333" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F333" s="5" t="s">
+      <c r="F333" s="2" t="s">
         <v>1270</v>
       </c>
-      <c r="G333" s="5" t="s">
+      <c r="G333" s="2" t="s">
         <v>1538</v>
       </c>
     </row>
@@ -14305,10 +14306,10 @@
       <c r="E334" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F334" s="5" t="s">
+      <c r="F334" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="G334" s="5" t="s">
+      <c r="G334" s="2" t="s">
         <v>1371</v>
       </c>
     </row>
@@ -14328,10 +14329,10 @@
       <c r="E335" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="F335" s="5" t="s">
+      <c r="F335" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="G335" s="5" t="s">
+      <c r="G335" s="2" t="s">
         <v>1539</v>
       </c>
     </row>
@@ -14351,10 +14352,10 @@
       <c r="E336" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="F336" s="5" t="s">
+      <c r="F336" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="G336" s="5" t="s">
+      <c r="G336" s="2" t="s">
         <v>1540</v>
       </c>
     </row>
@@ -14374,10 +14375,10 @@
       <c r="E337" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F337" s="5" t="s">
+      <c r="F337" s="2" t="s">
         <v>1273</v>
       </c>
-      <c r="G337" s="5" t="s">
+      <c r="G337" s="2" t="s">
         <v>1541</v>
       </c>
     </row>
@@ -14397,10 +14398,10 @@
       <c r="E338" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F338" s="5" t="s">
+      <c r="F338" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="G338" s="5" t="s">
+      <c r="G338" s="2" t="s">
         <v>1392</v>
       </c>
     </row>
@@ -14420,10 +14421,10 @@
       <c r="E339" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F339" s="5" t="s">
+      <c r="F339" s="2" t="s">
         <v>1274</v>
       </c>
-      <c r="G339" s="5" t="s">
+      <c r="G339" s="2" t="s">
         <v>1542</v>
       </c>
     </row>
@@ -14443,10 +14444,10 @@
       <c r="E340" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F340" s="5" t="s">
+      <c r="F340" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="G340" s="5" t="s">
+      <c r="G340" s="2" t="s">
         <v>1543</v>
       </c>
     </row>
@@ -14466,10 +14467,10 @@
       <c r="E341" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F341" s="5" t="s">
+      <c r="F341" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="G341" s="5" t="s">
+      <c r="G341" s="2" t="s">
         <v>1344</v>
       </c>
     </row>
@@ -14489,10 +14490,10 @@
       <c r="E342" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F342" s="5" t="s">
+      <c r="F342" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="G342" s="5" t="s">
+      <c r="G342" s="2" t="s">
         <v>1544</v>
       </c>
     </row>
@@ -14512,10 +14513,10 @@
       <c r="E343" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F343" s="5" t="s">
+      <c r="F343" s="2" t="s">
         <v>1277</v>
       </c>
-      <c r="G343" s="5" t="s">
+      <c r="G343" s="2" t="s">
         <v>1545</v>
       </c>
     </row>
@@ -14535,10 +14536,10 @@
       <c r="E344" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F344" s="5" t="s">
+      <c r="F344" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="G344" s="5" t="s">
+      <c r="G344" s="2" t="s">
         <v>1546</v>
       </c>
     </row>
@@ -14558,10 +14559,10 @@
       <c r="E345" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F345" s="5" t="s">
+      <c r="F345" s="2" t="s">
         <v>1279</v>
       </c>
-      <c r="G345" s="5" t="s">
+      <c r="G345" s="2" t="s">
         <v>1547</v>
       </c>
     </row>
@@ -14581,10 +14582,10 @@
       <c r="E346" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F346" s="5" t="s">
+      <c r="F346" s="2" t="s">
         <v>1280</v>
       </c>
-      <c r="G346" s="5" t="s">
+      <c r="G346" s="2" t="s">
         <v>1548</v>
       </c>
     </row>
@@ -14604,10 +14605,10 @@
       <c r="E347" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F347" s="5" t="s">
+      <c r="F347" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="G347" s="5" t="s">
+      <c r="G347" s="2" t="s">
         <v>1549</v>
       </c>
     </row>
@@ -14627,10 +14628,10 @@
       <c r="E348" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F348" s="5" t="s">
+      <c r="F348" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="G348" s="5" t="s">
+      <c r="G348" s="2" t="s">
         <v>1511</v>
       </c>
     </row>
@@ -14650,10 +14651,10 @@
       <c r="E349" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F349" s="5" t="s">
+      <c r="F349" s="2" t="s">
         <v>1282</v>
       </c>
-      <c r="G349" s="5" t="s">
+      <c r="G349" s="2" t="s">
         <v>1550</v>
       </c>
     </row>
@@ -14673,10 +14674,10 @@
       <c r="E350" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="F350" s="5" t="s">
+      <c r="F350" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="G350" s="5" t="s">
+      <c r="G350" s="2" t="s">
         <v>1540</v>
       </c>
     </row>
@@ -14696,10 +14697,10 @@
       <c r="E351" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F351" s="5" t="s">
+      <c r="F351" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="G351" s="5" t="s">
+      <c r="G351" s="2" t="s">
         <v>1551</v>
       </c>
     </row>
@@ -14719,10 +14720,10 @@
       <c r="E352" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F352" s="5" t="s">
+      <c r="F352" s="2" t="s">
         <v>1197</v>
       </c>
-      <c r="G352" s="5" t="s">
+      <c r="G352" s="2" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -14742,10 +14743,10 @@
       <c r="E353" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F353" s="5" t="s">
+      <c r="F353" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="G353" s="5" t="s">
+      <c r="G353" s="2" t="s">
         <v>1526</v>
       </c>
     </row>
@@ -14765,10 +14766,10 @@
       <c r="E354" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F354" s="5" t="s">
+      <c r="F354" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="G354" s="5" t="s">
+      <c r="G354" s="2" t="s">
         <v>1552</v>
       </c>
     </row>
@@ -14788,10 +14789,10 @@
       <c r="E355" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F355" s="5" t="s">
+      <c r="F355" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="G355" s="5" t="s">
+      <c r="G355" s="2" t="s">
         <v>1553</v>
       </c>
     </row>
@@ -14811,10 +14812,10 @@
       <c r="E356" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F356" s="5" t="s">
+      <c r="F356" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="G356" s="5" t="s">
+      <c r="G356" s="2" t="s">
         <v>1553</v>
       </c>
     </row>
@@ -14834,10 +14835,10 @@
       <c r="E357" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="F357" s="5" t="s">
+      <c r="F357" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="G357" s="5" t="s">
+      <c r="G357" s="2" t="s">
         <v>1554</v>
       </c>
     </row>
@@ -14857,10 +14858,10 @@
       <c r="E358" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F358" s="5" t="s">
+      <c r="F358" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="G358" s="5" t="s">
+      <c r="G358" s="2" t="s">
         <v>1465</v>
       </c>
     </row>
@@ -14880,10 +14881,10 @@
       <c r="E359" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F359" s="5" t="s">
+      <c r="F359" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="G359" s="5" t="s">
+      <c r="G359" s="2" t="s">
         <v>1555</v>
       </c>
     </row>
@@ -14903,10 +14904,10 @@
       <c r="E360" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="F360" s="5" t="s">
+      <c r="F360" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="G360" s="5" t="s">
+      <c r="G360" s="2" t="s">
         <v>1554</v>
       </c>
     </row>
@@ -14926,10 +14927,10 @@
       <c r="E361" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F361" s="5" t="s">
+      <c r="F361" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="G361" s="5" t="s">
+      <c r="G361" s="2" t="s">
         <v>1449</v>
       </c>
     </row>
@@ -14949,10 +14950,10 @@
       <c r="E362" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F362" s="5" t="s">
+      <c r="F362" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="G362" s="5" t="s">
+      <c r="G362" s="2" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -14972,10 +14973,10 @@
       <c r="E363" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F363" s="5" t="s">
+      <c r="F363" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="G363" s="5" t="s">
+      <c r="G363" s="2" t="s">
         <v>1549</v>
       </c>
     </row>
@@ -14995,10 +14996,10 @@
       <c r="E364" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F364" s="5" t="s">
+      <c r="F364" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="G364" s="5" t="s">
+      <c r="G364" s="2" t="s">
         <v>1556</v>
       </c>
     </row>
@@ -15018,10 +15019,10 @@
       <c r="E365" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F365" s="5" t="s">
+      <c r="F365" s="2" t="s">
         <v>1289</v>
       </c>
-      <c r="G365" s="5" t="s">
+      <c r="G365" s="2" t="s">
         <v>1557</v>
       </c>
     </row>
@@ -15041,10 +15042,10 @@
       <c r="E366" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F366" s="5" t="s">
+      <c r="F366" s="2" t="s">
         <v>1273</v>
       </c>
-      <c r="G366" s="5" t="s">
+      <c r="G366" s="2" t="s">
         <v>1541</v>
       </c>
     </row>
@@ -15064,10 +15065,10 @@
       <c r="E367" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F367" s="5" t="s">
+      <c r="F367" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="G367" s="5" t="s">
+      <c r="G367" s="2" t="s">
         <v>1558</v>
       </c>
     </row>
@@ -15087,10 +15088,10 @@
       <c r="E368" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F368" s="5" t="s">
+      <c r="F368" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="G368" s="5" t="s">
+      <c r="G368" s="2" t="s">
         <v>1558</v>
       </c>
     </row>
@@ -15110,10 +15111,10 @@
       <c r="E369" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F369" s="5" t="s">
+      <c r="F369" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="G369" s="5" t="s">
+      <c r="G369" s="2" t="s">
         <v>1543</v>
       </c>
     </row>
@@ -15133,10 +15134,10 @@
       <c r="E370" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F370" s="5" t="s">
+      <c r="F370" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="G370" s="5" t="s">
+      <c r="G370" s="2" t="s">
         <v>1341</v>
       </c>
     </row>
@@ -15156,10 +15157,10 @@
       <c r="E371" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F371" s="5" t="s">
+      <c r="F371" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="G371" s="5" t="s">
+      <c r="G371" s="2" t="s">
         <v>1559</v>
       </c>
     </row>
@@ -15179,10 +15180,10 @@
       <c r="E372" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F372" s="5" t="s">
+      <c r="F372" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="G372" s="5" t="s">
+      <c r="G372" s="2" t="s">
         <v>1483</v>
       </c>
     </row>
@@ -15202,10 +15203,10 @@
       <c r="E373" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F373" s="5" t="s">
+      <c r="F373" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="G373" s="5" t="s">
+      <c r="G373" s="2" t="s">
         <v>1437</v>
       </c>
     </row>
@@ -15225,10 +15226,10 @@
       <c r="E374" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="F374" s="5" t="s">
+      <c r="F374" s="2" t="s">
         <v>1292</v>
       </c>
-      <c r="G374" s="5" t="s">
+      <c r="G374" s="2" t="s">
         <v>1560</v>
       </c>
     </row>
@@ -15248,10 +15249,10 @@
       <c r="E375" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F375" s="5" t="s">
+      <c r="F375" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="G375" s="5" t="s">
+      <c r="G375" s="2" t="s">
         <v>1561</v>
       </c>
     </row>
@@ -15271,10 +15272,10 @@
       <c r="E376" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F376" s="5" t="s">
+      <c r="F376" s="2" t="s">
         <v>1294</v>
       </c>
-      <c r="G376" s="5" t="s">
+      <c r="G376" s="2" t="s">
         <v>1562</v>
       </c>
     </row>
@@ -15294,10 +15295,10 @@
       <c r="E377" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F377" s="5" t="s">
+      <c r="F377" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="G377" s="5" t="s">
+      <c r="G377" s="2" t="s">
         <v>1563</v>
       </c>
     </row>
@@ -15317,10 +15318,10 @@
       <c r="E378" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F378" s="5" t="s">
+      <c r="F378" s="2" t="s">
         <v>1296</v>
       </c>
-      <c r="G378" s="5" t="s">
+      <c r="G378" s="2" t="s">
         <v>1564</v>
       </c>
     </row>
@@ -15340,10 +15341,10 @@
       <c r="E379" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F379" s="5" t="s">
+      <c r="F379" s="2" t="s">
         <v>1219</v>
       </c>
-      <c r="G379" s="5" t="s">
+      <c r="G379" s="2" t="s">
         <v>1488</v>
       </c>
     </row>
@@ -15363,10 +15364,10 @@
       <c r="E380" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F380" s="5" t="s">
+      <c r="F380" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="G380" s="5" t="s">
+      <c r="G380" s="2" t="s">
         <v>1478</v>
       </c>
     </row>
@@ -15386,10 +15387,10 @@
       <c r="E381" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F381" s="5" t="s">
+      <c r="F381" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="G381" s="5" t="s">
+      <c r="G381" s="2" t="s">
         <v>1534</v>
       </c>
     </row>
@@ -15409,10 +15410,10 @@
       <c r="E382" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F382" s="5" t="s">
+      <c r="F382" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="G382" s="5" t="s">
+      <c r="G382" s="2" t="s">
         <v>1448</v>
       </c>
     </row>
@@ -15432,10 +15433,10 @@
       <c r="E383" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F383" s="5" t="s">
+      <c r="F383" s="2" t="s">
         <v>1297</v>
       </c>
-      <c r="G383" s="5" t="s">
+      <c r="G383" s="2" t="s">
         <v>1565</v>
       </c>
     </row>
@@ -15455,10 +15456,10 @@
       <c r="E384" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F384" s="5" t="s">
+      <c r="F384" s="2" t="s">
         <v>1298</v>
       </c>
-      <c r="G384" s="5" t="s">
+      <c r="G384" s="2" t="s">
         <v>1566</v>
       </c>
     </row>
@@ -15478,10 +15479,10 @@
       <c r="E385" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F385" s="5" t="s">
+      <c r="F385" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="G385" s="5" t="s">
+      <c r="G385" s="2" t="s">
         <v>1567</v>
       </c>
     </row>
@@ -15501,10 +15502,10 @@
       <c r="E386" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="F386" s="5" t="s">
+      <c r="F386" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="G386" s="5" t="s">
+      <c r="G386" s="2" t="s">
         <v>1568</v>
       </c>
     </row>
@@ -15524,10 +15525,10 @@
       <c r="E387" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F387" s="5" t="s">
+      <c r="F387" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="G387" s="5" t="s">
+      <c r="G387" s="2" t="s">
         <v>1507</v>
       </c>
     </row>
@@ -15547,10 +15548,10 @@
       <c r="E388" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F388" s="5" t="s">
+      <c r="F388" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="G388" s="5" t="s">
+      <c r="G388" s="2" t="s">
         <v>1347</v>
       </c>
     </row>
@@ -15570,10 +15571,10 @@
       <c r="E389" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F389" s="5" t="s">
+      <c r="F389" s="2" t="s">
         <v>1301</v>
       </c>
-      <c r="G389" s="5" t="s">
+      <c r="G389" s="2" t="s">
         <v>1569</v>
       </c>
     </row>
@@ -15593,10 +15594,10 @@
       <c r="E390" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F390" s="5" t="s">
+      <c r="F390" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="G390" s="5" t="s">
+      <c r="G390" s="2" t="s">
         <v>1546</v>
       </c>
     </row>
@@ -15616,10 +15617,10 @@
       <c r="E391" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F391" s="5" t="s">
+      <c r="F391" s="2" t="s">
         <v>1302</v>
       </c>
-      <c r="G391" s="5" t="s">
+      <c r="G391" s="2" t="s">
         <v>1570</v>
       </c>
     </row>
@@ -15639,10 +15640,10 @@
       <c r="E392" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F392" s="5" t="s">
+      <c r="F392" s="2" t="s">
         <v>1303</v>
       </c>
-      <c r="G392" s="5" t="s">
+      <c r="G392" s="2" t="s">
         <v>1571</v>
       </c>
     </row>
@@ -15662,10 +15663,10 @@
       <c r="E393" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F393" s="5" t="s">
+      <c r="F393" s="2" t="s">
         <v>1274</v>
       </c>
-      <c r="G393" s="5" t="s">
+      <c r="G393" s="2" t="s">
         <v>1542</v>
       </c>
     </row>
@@ -15685,10 +15686,10 @@
       <c r="E394" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F394" s="5" t="s">
+      <c r="F394" s="2" t="s">
         <v>1270</v>
       </c>
-      <c r="G394" s="5" t="s">
+      <c r="G394" s="2" t="s">
         <v>1538</v>
       </c>
     </row>
@@ -15708,10 +15709,10 @@
       <c r="E395" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F395" s="5" t="s">
+      <c r="F395" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="G395" s="5" t="s">
+      <c r="G395" s="2" t="s">
         <v>1484</v>
       </c>
     </row>
@@ -15731,10 +15732,10 @@
       <c r="E396" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F396" s="5" t="s">
+      <c r="F396" s="2" t="s">
         <v>1279</v>
       </c>
-      <c r="G396" s="5" t="s">
+      <c r="G396" s="2" t="s">
         <v>1547</v>
       </c>
     </row>
@@ -15754,10 +15755,10 @@
       <c r="E397" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F397" s="5" t="s">
+      <c r="F397" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="G397" s="5" t="s">
+      <c r="G397" s="2" t="s">
         <v>1544</v>
       </c>
     </row>
@@ -15777,10 +15778,10 @@
       <c r="E398" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F398" s="5" t="s">
+      <c r="F398" s="2" t="s">
         <v>1304</v>
       </c>
-      <c r="G398" s="5" t="s">
+      <c r="G398" s="2" t="s">
         <v>1572</v>
       </c>
     </row>
@@ -15800,10 +15801,10 @@
       <c r="E399" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F399" s="5" t="s">
+      <c r="F399" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="G399" s="5" t="s">
+      <c r="G399" s="2" t="s">
         <v>1524</v>
       </c>
     </row>
@@ -15823,10 +15824,10 @@
       <c r="E400" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F400" s="5" t="s">
+      <c r="F400" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="G400" s="5" t="s">
+      <c r="G400" s="2" t="s">
         <v>1531</v>
       </c>
     </row>
@@ -15846,10 +15847,10 @@
       <c r="E401" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F401" s="5" t="s">
+      <c r="F401" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G401" s="5" t="s">
+      <c r="G401" s="2" t="s">
         <v>1374</v>
       </c>
     </row>
@@ -15869,10 +15870,10 @@
       <c r="E402" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F402" s="5" t="s">
+      <c r="F402" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="G402" s="5" t="s">
+      <c r="G402" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -15892,10 +15893,10 @@
       <c r="E403" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F403" s="5" t="s">
+      <c r="F403" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="G403" s="5" t="s">
+      <c r="G403" s="2" t="s">
         <v>1574</v>
       </c>
     </row>
@@ -15915,10 +15916,10 @@
       <c r="E404" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F404" s="5" t="s">
+      <c r="F404" s="2" t="s">
         <v>1306</v>
       </c>
-      <c r="G404" s="5" t="s">
+      <c r="G404" s="2" t="s">
         <v>1574</v>
       </c>
     </row>
@@ -15938,10 +15939,10 @@
       <c r="E405" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F405" s="5" t="s">
+      <c r="F405" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="G405" s="5" t="s">
+      <c r="G405" s="2" t="s">
         <v>1575</v>
       </c>
     </row>
@@ -15961,10 +15962,10 @@
       <c r="E406" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F406" s="5" t="s">
+      <c r="F406" s="2" t="s">
         <v>1308</v>
       </c>
-      <c r="G406" s="5" t="s">
+      <c r="G406" s="2" t="s">
         <v>1576</v>
       </c>
     </row>
@@ -15984,10 +15985,10 @@
       <c r="E407" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="F407" s="5" t="s">
+      <c r="F407" s="2" t="s">
         <v>1309</v>
       </c>
-      <c r="G407" s="5" t="s">
+      <c r="G407" s="2" t="s">
         <v>1577</v>
       </c>
     </row>
@@ -16007,10 +16008,10 @@
       <c r="E408" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F408" s="5" t="s">
+      <c r="F408" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="G408" s="5" t="s">
+      <c r="G408" s="2" t="s">
         <v>1490</v>
       </c>
     </row>
@@ -16030,10 +16031,10 @@
       <c r="E409" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F409" s="5" t="s">
+      <c r="F409" s="2" t="s">
         <v>1310</v>
       </c>
-      <c r="G409" s="5" t="s">
+      <c r="G409" s="2" t="s">
         <v>1578</v>
       </c>
     </row>
@@ -16053,10 +16054,10 @@
       <c r="E410" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F410" s="5" t="s">
+      <c r="F410" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="G410" s="5" t="s">
+      <c r="G410" s="2" t="s">
         <v>1457</v>
       </c>
     </row>
@@ -16076,10 +16077,10 @@
       <c r="E411" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="F411" s="5" t="s">
+      <c r="F411" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="G411" s="5" t="s">
+      <c r="G411" s="2" t="s">
         <v>1579</v>
       </c>
     </row>
@@ -16099,10 +16100,10 @@
       <c r="E412" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="F412" s="5" t="s">
+      <c r="F412" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G412" s="5" t="s">
+      <c r="G412" s="2" t="s">
         <v>1580</v>
       </c>
     </row>
@@ -16122,10 +16123,10 @@
       <c r="E413" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F413" s="5" t="s">
+      <c r="F413" s="2" t="s">
         <v>1313</v>
       </c>
-      <c r="G413" s="5" t="s">
+      <c r="G413" s="2" t="s">
         <v>1581</v>
       </c>
     </row>
@@ -16145,10 +16146,10 @@
       <c r="E414" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F414" s="5" t="s">
+      <c r="F414" s="2" t="s">
         <v>1314</v>
       </c>
-      <c r="G414" s="5" t="s">
+      <c r="G414" s="2" t="s">
         <v>1582</v>
       </c>
     </row>
@@ -16168,10 +16169,10 @@
       <c r="E415" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F415" s="5" t="s">
+      <c r="F415" s="2" t="s">
         <v>1315</v>
       </c>
-      <c r="G415" s="5" t="s">
+      <c r="G415" s="2" t="s">
         <v>1583</v>
       </c>
     </row>
@@ -16191,10 +16192,10 @@
       <c r="E416" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F416" s="5" t="s">
+      <c r="F416" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="G416" s="5" t="s">
+      <c r="G416" s="2" t="s">
         <v>1584</v>
       </c>
     </row>
@@ -16214,10 +16215,10 @@
       <c r="E417" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F417" s="5" t="s">
+      <c r="F417" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="G417" s="5" t="s">
+      <c r="G417" s="2" t="s">
         <v>1511</v>
       </c>
     </row>
@@ -16237,10 +16238,10 @@
       <c r="E418" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F418" s="5" t="s">
+      <c r="F418" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="G418" s="5" t="s">
+      <c r="G418" s="2" t="s">
         <v>1534</v>
       </c>
     </row>
@@ -16260,10 +16261,10 @@
       <c r="E419" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F419" s="5" t="s">
+      <c r="F419" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="G419" s="5" t="s">
+      <c r="G419" s="2" t="s">
         <v>1394</v>
       </c>
     </row>
@@ -16283,10 +16284,10 @@
       <c r="E420" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F420" s="5" t="s">
+      <c r="F420" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="G420" s="5" t="s">
+      <c r="G420" s="2" t="s">
         <v>1552</v>
       </c>
     </row>
@@ -16306,10 +16307,10 @@
       <c r="E421" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F421" s="5" t="s">
+      <c r="F421" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="G421" s="5" t="s">
+      <c r="G421" s="2" t="s">
         <v>1585</v>
       </c>
     </row>
@@ -16329,10 +16330,10 @@
       <c r="E422" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="F422" s="5" t="s">
+      <c r="F422" s="2" t="s">
         <v>1318</v>
       </c>
-      <c r="G422" s="5" t="s">
+      <c r="G422" s="2" t="s">
         <v>1586</v>
       </c>
     </row>
@@ -16352,10 +16353,10 @@
       <c r="E423" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F423" s="5" t="s">
+      <c r="F423" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="G423" s="5" t="s">
+      <c r="G423" s="2" t="s">
         <v>1587</v>
       </c>
     </row>
@@ -16375,10 +16376,10 @@
       <c r="E424" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F424" s="5" t="s">
+      <c r="F424" s="2" t="s">
         <v>1320</v>
       </c>
-      <c r="G424" s="5" t="s">
+      <c r="G424" s="2" t="s">
         <v>1588</v>
       </c>
     </row>
@@ -16398,10 +16399,10 @@
       <c r="E425" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="F425" s="5" t="s">
+      <c r="F425" s="2" t="s">
         <v>1321</v>
       </c>
-      <c r="G425" s="5" t="s">
+      <c r="G425" s="2" t="s">
         <v>1589</v>
       </c>
     </row>
@@ -16421,10 +16422,10 @@
       <c r="E426" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F426" s="5" t="s">
+      <c r="F426" s="2" t="s">
         <v>1322</v>
       </c>
-      <c r="G426" s="5" t="s">
+      <c r="G426" s="2" t="s">
         <v>1590</v>
       </c>
     </row>
@@ -16444,10 +16445,10 @@
       <c r="E427" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="F427" s="5" t="s">
+      <c r="F427" s="2" t="s">
         <v>1323</v>
       </c>
-      <c r="G427" s="5" t="s">
+      <c r="G427" s="2" t="s">
         <v>1591</v>
       </c>
     </row>
@@ -16467,10 +16468,10 @@
       <c r="E428" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="F428" s="5" t="s">
+      <c r="F428" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="G428" s="5" t="s">
+      <c r="G428" s="2" t="s">
         <v>1579</v>
       </c>
     </row>
@@ -16490,10 +16491,10 @@
       <c r="E429" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="F429" s="5" t="s">
+      <c r="F429" s="2" t="s">
         <v>1324</v>
       </c>
-      <c r="G429" s="5" t="s">
+      <c r="G429" s="2" t="s">
         <v>1592</v>
       </c>
     </row>
@@ -16513,10 +16514,10 @@
       <c r="E430" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F430" s="5" t="s">
+      <c r="F430" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="G430" s="5" t="s">
+      <c r="G430" s="2" t="s">
         <v>1559</v>
       </c>
     </row>
@@ -16536,10 +16537,10 @@
       <c r="E431" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F431" s="5" t="s">
+      <c r="F431" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="G431" s="5" t="s">
+      <c r="G431" s="2" t="s">
         <v>1567</v>
       </c>
     </row>
@@ -16559,10 +16560,10 @@
       <c r="E432" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F432" s="5" t="s">
+      <c r="F432" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="G432" s="5" t="s">
+      <c r="G432" s="2" t="s">
         <v>1325</v>
       </c>
     </row>
@@ -16582,10 +16583,10 @@
       <c r="E433" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F433" s="5" t="s">
+      <c r="F433" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G433" s="5" t="s">
+      <c r="G433" s="2" t="s">
         <v>1593</v>
       </c>
     </row>
@@ -16605,10 +16606,10 @@
       <c r="E434" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F434" s="5" t="s">
+      <c r="F434" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="G434" s="5" t="s">
+      <c r="G434" s="2" t="s">
         <v>1594</v>
       </c>
     </row>
@@ -16628,10 +16629,10 @@
       <c r="E435" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F435" s="5" t="s">
+      <c r="F435" s="2" t="s">
         <v>1277</v>
       </c>
-      <c r="G435" s="5" t="s">
+      <c r="G435" s="2" t="s">
         <v>1545</v>
       </c>
     </row>
@@ -16651,10 +16652,10 @@
       <c r="E436" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F436" s="5" t="s">
+      <c r="F436" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="G436" s="5" t="s">
+      <c r="G436" s="2" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -16674,10 +16675,10 @@
       <c r="E437" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F437" s="5" t="s">
+      <c r="F437" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="G437" s="5" t="s">
+      <c r="G437" s="2" t="s">
         <v>1595</v>
       </c>
     </row>
@@ -16697,10 +16698,10 @@
       <c r="E438" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F438" s="5" t="s">
+      <c r="F438" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="G438" s="5" t="s">
+      <c r="G438" s="2" t="s">
         <v>1596</v>
       </c>
     </row>
@@ -16720,10 +16721,10 @@
       <c r="E439" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F439" s="5" t="s">
+      <c r="F439" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="G439" s="5" t="s">
+      <c r="G439" s="2" t="s">
         <v>1597</v>
       </c>
     </row>
@@ -16743,10 +16744,10 @@
       <c r="E440" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F440" s="5" t="s">
+      <c r="F440" s="2" t="s">
         <v>1330</v>
       </c>
-      <c r="G440" s="5" t="s">
+      <c r="G440" s="2" t="s">
         <v>1598</v>
       </c>
     </row>
@@ -16766,10 +16767,10 @@
       <c r="E441" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F441" s="5" t="s">
+      <c r="F441" s="2" t="s">
         <v>1331</v>
       </c>
-      <c r="G441" s="5" t="s">
+      <c r="G441" s="2" t="s">
         <v>1599</v>
       </c>
     </row>
@@ -16789,10 +16790,10 @@
       <c r="E442" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F442" s="5" t="s">
+      <c r="F442" s="2" t="s">
         <v>1331</v>
       </c>
-      <c r="G442" s="5" t="s">
+      <c r="G442" s="2" t="s">
         <v>1599</v>
       </c>
     </row>
@@ -16812,10 +16813,10 @@
       <c r="E443" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F443" s="5" t="s">
+      <c r="F443" s="2" t="s">
         <v>1332</v>
       </c>
-      <c r="G443" s="5" t="s">
+      <c r="G443" s="2" t="s">
         <v>1600</v>
       </c>
     </row>
@@ -16835,10 +16836,10 @@
       <c r="E444" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F444" s="5" t="s">
+      <c r="F444" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="G444" s="5" t="s">
+      <c r="G444" s="2" t="s">
         <v>1601</v>
       </c>
     </row>
@@ -16858,10 +16859,10 @@
       <c r="E445" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F445" s="5" t="s">
+      <c r="F445" s="2" t="s">
         <v>1334</v>
       </c>
-      <c r="G445" s="5" t="s">
+      <c r="G445" s="2" t="s">
         <v>1334</v>
       </c>
     </row>
@@ -16881,10 +16882,10 @@
       <c r="E446" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F446" s="5" t="s">
+      <c r="F446" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="G446" s="5" t="s">
+      <c r="G446" s="2" t="s">
         <v>1602</v>
       </c>
     </row>
@@ -16904,10 +16905,10 @@
       <c r="E447" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F447" s="5" t="s">
+      <c r="F447" s="2" t="s">
         <v>1336</v>
       </c>
-      <c r="G447" s="5" t="s">
+      <c r="G447" s="2" t="s">
         <v>1603</v>
       </c>
     </row>
@@ -16927,10 +16928,10 @@
       <c r="E448" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F448" s="5" t="s">
+      <c r="F448" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="G448" s="5" t="s">
+      <c r="G448" s="2" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -16950,10 +16951,10 @@
       <c r="E449" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="F449" s="5" t="s">
+      <c r="F449" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="G449" s="5" t="s">
+      <c r="G449" s="2" t="s">
         <v>1604</v>
       </c>
     </row>
@@ -16973,10 +16974,10 @@
       <c r="E450" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="F450" s="5" t="s">
+      <c r="F450" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="G450" s="5" t="s">
+      <c r="G450" s="2" t="s">
         <v>1605</v>
       </c>
     </row>
@@ -16996,10 +16997,10 @@
       <c r="E451" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="F451" s="5" t="s">
+      <c r="F451" s="2" t="s">
         <v>1338</v>
       </c>
-      <c r="G451" s="5" t="s">
+      <c r="G451" s="2" t="s">
         <v>1606</v>
       </c>
     </row>
@@ -17019,10 +17020,10 @@
       <c r="E452" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F452" s="5" t="s">
+      <c r="F452" s="2" t="s">
         <v>1339</v>
       </c>
-      <c r="G452" s="5" t="s">
+      <c r="G452" s="2" t="s">
         <v>1607</v>
       </c>
     </row>
@@ -17042,10 +17043,10 @@
       <c r="E453" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="F453" s="5" t="s">
+      <c r="F453" s="2" t="s">
         <v>1340</v>
       </c>
-      <c r="G453" s="5" t="s">
+      <c r="G453" s="2" t="s">
         <v>1608</v>
       </c>
     </row>
